--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92B27EBF-F8A0-4451-910B-9D6DC9492626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2928B1EA-05F9-4301-8D23-2A7E76DFFFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{DB0057FC-08A0-4573-AD6A-33DE9E5EBBA7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{A4ED0998-8CA2-4613-90B1-80DE0A7612EC}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="599">
   <si>
     <t>~tradelinks_dins</t>
   </si>
@@ -735,7 +738,7 @@
     <t>grid link -66.0 km- way/158232924-220;way/180535363-220 (thermal x 0.7 N-1)</t>
   </si>
   <si>
-    <t>~commodity_geo</t>
+    <t>~commodity_geo:network=electricity</t>
   </si>
   <si>
     <t>commodity</t>
@@ -1116,15 +1119,9 @@
     <t>elc_won_POL_005</t>
   </si>
   <si>
-    <t>POLYGON ((17.762656 51.01968, 17.762656 51.46934, 18.448578 51.46934, 18.448578 51.01968, 17.762656 51.01968))</t>
-  </si>
-  <si>
     <t>elc_won_POL_006</t>
   </si>
   <si>
-    <t>POLYGON ((16.390811 50.570019, 16.390811 51.01968, 17.076733 51.01968, 17.076733 50.570019, 17.076733 50.120359, 16.390811 50.120359, 16.390811 50.570019))</t>
-  </si>
-  <si>
     <t>elc_won_POL_007</t>
   </si>
   <si>
@@ -1137,9 +1134,6 @@
     <t>elc_won_POL_010</t>
   </si>
   <si>
-    <t>POLYGON ((14.333045 51.01968, 15.018967 51.01968, 15.018967 51.46934, 15.704889 51.46934, 15.704889 51.01968, 15.704889 50.570019, 15.018967 50.570019, 14.333045 50.570019, 14.333045 51.01968))</t>
-  </si>
-  <si>
     <t>elc_won_POL_011</t>
   </si>
   <si>
@@ -1167,9 +1161,6 @@
     <t>elc_won_POL_019</t>
   </si>
   <si>
-    <t>POLYGON ((22.564111 50.570019, 22.564111 51.01968, 23.250033 51.01968, 23.935955 51.01968, 23.935955 50.570019, 23.935955 50.120359, 23.250033 50.120359, 23.250033 49.670699, 22.564111 49.670699, 22.564111 50.120359, 22.564111 50.570019))</t>
-  </si>
-  <si>
     <t>elc_won_POL_020</t>
   </si>
   <si>
@@ -1224,9 +1215,6 @@
     <t>elc_won_POL_037</t>
   </si>
   <si>
-    <t>MULTIPOLYGON (((17.076733 50.120359, 17.762656 50.120359, 17.762656 49.670699, 17.076733 49.670699, 17.076733 50.120359)), ((17.762656 51.01968, 18.448578 51.01968, 18.448578 50.570019, 18.448578 50.120359, 17.762656 50.120359, 17.762656 50.570019, 17.762656 51.01968)))</t>
-  </si>
-  <si>
     <t>elc_won_POL_038</t>
   </si>
   <si>
@@ -1248,12 +1236,18 @@
     <t>elc_won_POL_044</t>
   </si>
   <si>
-    <t>POLYGON ((19.820422 50.120359, 19.820422 50.570019, 20.506344 50.570019, 20.506344 50.120359, 19.820422 50.120359))</t>
-  </si>
-  <si>
     <t>elc_won_POL_045</t>
   </si>
   <si>
+    <t>elc_won_POL_046</t>
+  </si>
+  <si>
+    <t>elc_won_POL_047</t>
+  </si>
+  <si>
+    <t>elc_won_POL_048</t>
+  </si>
+  <si>
     <t>co2</t>
   </si>
   <si>
@@ -1840,6 +1834,9 @@
   </si>
   <si>
     <t>co2 pipeline -46 km- way/29115701-220 to T7</t>
+  </si>
+  <si>
+    <t>~commodity_geo:network=co2</t>
   </si>
 </sst>
 </file>
@@ -1850,7 +1847,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1905,39 +1902,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1989,7 +1986,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2100,13 +2097,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -2115,6 +2105,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2179,19 +2176,39 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF917C8-41ED-474A-8F99-9C8CB2D6B467}">
-  <dimension ref="B3:S155"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7EFE7B4-66F0-4EF1-A6DE-FE09F6A8A9E7}">
+  <dimension ref="B3:S158"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:19" x14ac:dyDescent="0.45">
@@ -4252,10 +4269,10 @@
         <v>8</v>
       </c>
       <c r="Q53">
-        <v>17.732742320902791</v>
+        <v>17.547809697404155</v>
       </c>
       <c r="R53">
-        <v>53.197615562848213</v>
+        <v>53.043150454655695</v>
       </c>
       <c r="S53" t="s">
         <v>239</v>
@@ -4296,10 +4313,10 @@
         <v>8</v>
       </c>
       <c r="Q54">
-        <v>23.076741255143787</v>
+        <v>23.133301060688336</v>
       </c>
       <c r="R54">
-        <v>52.887133598646692</v>
+        <v>53.187251027326219</v>
       </c>
       <c r="S54" t="s">
         <v>241</v>
@@ -4340,10 +4357,10 @@
         <v>8</v>
       </c>
       <c r="Q55">
-        <v>15.18361928372261</v>
+        <v>14.879031900155717</v>
       </c>
       <c r="R55">
-        <v>52.800197329771187</v>
+        <v>52.593490272793417</v>
       </c>
       <c r="S55" t="s">
         <v>243</v>
@@ -4384,10 +4401,10 @@
         <v>8</v>
       </c>
       <c r="Q56">
-        <v>16.443817708345744</v>
+        <v>16.047850156734548</v>
       </c>
       <c r="R56">
-        <v>51.286279433186863</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S56" t="s">
         <v>245</v>
@@ -4428,10 +4445,10 @@
         <v>8</v>
       </c>
       <c r="Q57">
-        <v>17.573992401991987</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R57">
-        <v>50.896000389817708</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S57" t="s">
         <v>247</v>
@@ -4472,10 +4489,10 @@
         <v>8</v>
       </c>
       <c r="Q58">
-        <v>16.733772344126869</v>
+        <v>16.700680826967581</v>
       </c>
       <c r="R58">
-        <v>50.670886022355177</v>
+        <v>50.20437696578923</v>
       </c>
       <c r="S58" t="s">
         <v>249</v>
@@ -4604,10 +4621,10 @@
         <v>8</v>
       </c>
       <c r="Q61">
-        <v>20.474987843539957</v>
+        <v>20.701782962343</v>
       </c>
       <c r="R61">
-        <v>53.867432812752376</v>
+        <v>54.18832903488137</v>
       </c>
       <c r="S61" t="s">
         <v>255</v>
@@ -4648,10 +4665,10 @@
         <v>8</v>
       </c>
       <c r="Q62">
-        <v>15.346251681111026</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="R62">
-        <v>51.202873879217471</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S62" t="s">
         <v>257</v>
@@ -4692,10 +4709,10 @@
         <v>8</v>
       </c>
       <c r="Q63">
-        <v>18.73472341078692</v>
+        <v>18.782950053433741</v>
       </c>
       <c r="R63">
-        <v>54.02228256102228</v>
+        <v>53.942470818380237</v>
       </c>
       <c r="S63" t="s">
         <v>259</v>
@@ -4736,10 +4753,10 @@
         <v>8</v>
       </c>
       <c r="Q64">
-        <v>21.804009726719805</v>
+        <v>21.887953266623537</v>
       </c>
       <c r="R64">
-        <v>52.847999678035883</v>
+        <v>53.014105550648793</v>
       </c>
       <c r="S64" t="s">
         <v>261</v>
@@ -4780,10 +4797,10 @@
         <v>8</v>
       </c>
       <c r="Q65">
-        <v>15.169582070037247</v>
+        <v>14.875712340153196</v>
       </c>
       <c r="R65">
-        <v>51.911584313619549</v>
+        <v>51.892398915433461</v>
       </c>
       <c r="S65" t="s">
         <v>263</v>
@@ -4824,10 +4841,10 @@
         <v>8</v>
       </c>
       <c r="Q66">
-        <v>15.343911278165097</v>
+        <v>14.904646511080676</v>
       </c>
       <c r="R66">
-        <v>53.930659874252505</v>
+        <v>53.792584091092806</v>
       </c>
       <c r="S66" t="s">
         <v>265</v>
@@ -4868,10 +4885,10 @@
         <v>8</v>
       </c>
       <c r="Q67">
-        <v>21.686893606685583</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R67">
-        <v>49.748425318724088</v>
+        <v>49.445868999757522</v>
       </c>
       <c r="S67" t="s">
         <v>267</v>
@@ -4912,10 +4929,10 @@
         <v>8</v>
       </c>
       <c r="Q68">
-        <v>22.600054496319373</v>
+        <v>22.603515833460445</v>
       </c>
       <c r="R68">
-        <v>54.004982398083385</v>
+        <v>54.312064653523798</v>
       </c>
       <c r="S68" t="s">
         <v>269</v>
@@ -4956,10 +4973,10 @@
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>19.728152585549065</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R69">
-        <v>51.550412267890401</v>
+        <v>51.244509727206612</v>
       </c>
       <c r="S69" t="s">
         <v>271</v>
@@ -5003,7 +5020,7 @@
         <v>18.791538906303831</v>
       </c>
       <c r="R70">
-        <v>51.419955039622174</v>
+        <v>51.690437204601821</v>
       </c>
       <c r="S70" t="s">
         <v>273</v>
@@ -5044,10 +5061,10 @@
         <v>8</v>
       </c>
       <c r="Q71">
-        <v>23.099272843498948</v>
+        <v>23.592994218050087</v>
       </c>
       <c r="R71">
-        <v>50.260453695040219</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S71" t="s">
         <v>275</v>
@@ -5088,10 +5105,10 @@
         <v>8</v>
       </c>
       <c r="Q72">
-        <v>16.490596872499417</v>
+        <v>16.349304708128344</v>
       </c>
       <c r="R72">
-        <v>53.766733588287018</v>
+        <v>53.94247081838023</v>
       </c>
       <c r="S72" t="s">
         <v>277</v>
@@ -5135,7 +5152,7 @@
         <v>16.047850156734548</v>
       </c>
       <c r="R73">
-        <v>51.819832365173717</v>
+        <v>51.919000000000011</v>
       </c>
       <c r="S73" t="s">
         <v>279</v>
@@ -5220,10 +5237,10 @@
         <v>8</v>
       </c>
       <c r="Q75">
-        <v>20.849305468480804</v>
+        <v>20.8493054684808</v>
       </c>
       <c r="R75">
-        <v>50.224675331577139</v>
+        <v>49.8599303133334</v>
       </c>
       <c r="S75" t="s">
         <v>283</v>
@@ -5264,10 +5281,10 @@
         <v>8</v>
       </c>
       <c r="Q76">
-        <v>23.198875657127921</v>
+        <v>23.486875120767376</v>
       </c>
       <c r="R76">
-        <v>51.540282380815263</v>
+        <v>51.710185794668313</v>
       </c>
       <c r="S76" t="s">
         <v>285</v>
@@ -5352,10 +5369,10 @@
         <v>8</v>
       </c>
       <c r="Q78">
-        <v>20.45513220923721</v>
+        <v>20.164133104060543</v>
       </c>
       <c r="R78">
-        <v>50.996290709060048</v>
+        <v>51.018998941964419</v>
       </c>
       <c r="S78" t="s">
         <v>289</v>
@@ -5443,7 +5460,7 @@
         <v>22.221149843265444</v>
       </c>
       <c r="R80">
-        <v>50.466416149028909</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S80" t="s">
         <v>293</v>
@@ -5484,10 +5501,10 @@
         <v>8</v>
       </c>
       <c r="Q81">
-        <v>19.133601934620422</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R81">
-        <v>50.794849545344327</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S81" t="s">
         <v>295</v>
@@ -5528,10 +5545,10 @@
         <v>8</v>
       </c>
       <c r="Q82">
-        <v>18.791538906303828</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R82">
-        <v>52.858257807793557</v>
+        <v>53.043150454655688</v>
       </c>
       <c r="S82" t="s">
         <v>297</v>
@@ -5575,7 +5592,7 @@
         <v>21.535227655873118</v>
       </c>
       <c r="R83">
-        <v>51.028817664495243</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S83" t="s">
         <v>299</v>
@@ -5660,10 +5677,10 @@
         <v>8</v>
       </c>
       <c r="Q85">
-        <v>18.200403953900462</v>
+        <v>18.105616718911509</v>
       </c>
       <c r="R85">
-        <v>52.169564808191033</v>
+        <v>52.143830090931147</v>
       </c>
       <c r="S85" t="s">
         <v>303</v>
@@ -5748,10 +5765,10 @@
         <v>8</v>
       </c>
       <c r="Q87">
-        <v>21.031789374844319</v>
+        <v>21.135688356956784</v>
       </c>
       <c r="R87">
-        <v>52.28019358068476</v>
+        <v>52.239739576014692</v>
       </c>
       <c r="S87" t="s">
         <v>307</v>
@@ -5836,10 +5853,10 @@
         <v>8</v>
       </c>
       <c r="Q89">
-        <v>21.866802774911854</v>
+        <v>21.708559845867718</v>
       </c>
       <c r="R89">
-        <v>53.775203125121777</v>
+        <v>54.126240919490058</v>
       </c>
       <c r="S89" t="s">
         <v>311</v>
@@ -5853,10 +5870,10 @@
         <v>8</v>
       </c>
       <c r="Q90">
-        <v>16.65132373540435</v>
+        <v>16.559716621285517</v>
       </c>
       <c r="R90">
-        <v>52.707053608818114</v>
+        <v>53.043150454655688</v>
       </c>
       <c r="S90" t="s">
         <v>313</v>
@@ -5870,10 +5887,10 @@
         <v>8</v>
       </c>
       <c r="Q91">
-        <v>18.102430082591109</v>
+        <v>18.105616718911509</v>
       </c>
       <c r="R91">
-        <v>50.368478771061248</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S91" t="s">
         <v>315</v>
@@ -5921,10 +5938,10 @@
         <v>8</v>
       </c>
       <c r="Q94">
-        <v>19.475481690054949</v>
+        <v>19.439611648373191</v>
       </c>
       <c r="R94">
-        <v>49.872151522293322</v>
+        <v>49.720309400782064</v>
       </c>
       <c r="S94" t="s">
         <v>321</v>
@@ -5938,10 +5955,10 @@
         <v>8</v>
       </c>
       <c r="Q95">
-        <v>19.163221535912964</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R95">
-        <v>53.736469293282624</v>
+        <v>53.942470818380237</v>
       </c>
       <c r="S95" t="s">
         <v>323</v>
@@ -5955,10 +5972,10 @@
         <v>8</v>
       </c>
       <c r="Q96">
-        <v>19.907650709888724</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R96">
-        <v>52.581850669181293</v>
+        <v>52.593490272793417</v>
       </c>
       <c r="S96" t="s">
         <v>325</v>
@@ -5975,7 +5992,7 @@
         <v>17.419694531519191</v>
       </c>
       <c r="R97">
-        <v>51.351016228937411</v>
+        <v>51.244509727206605</v>
       </c>
       <c r="S97" t="s">
         <v>327</v>
@@ -6006,10 +6023,10 @@
         <v>8</v>
       </c>
       <c r="Q99">
-        <v>20.163383281088478</v>
+        <v>20.163383281088475</v>
       </c>
       <c r="R99">
-        <v>50.11164519658584</v>
+        <v>49.598802215787757</v>
       </c>
       <c r="S99" t="s">
         <v>331</v>
@@ -6023,10 +6040,10 @@
         <v>8</v>
       </c>
       <c r="Q100">
-        <v>22.033984475568818</v>
+        <v>22.178267215011683</v>
       </c>
       <c r="R100">
-        <v>51.717686603776322</v>
+        <v>51.90882588090858</v>
       </c>
       <c r="S100" t="s">
         <v>333</v>
@@ -6210,10 +6227,10 @@
         <v>8</v>
       </c>
       <c r="Q111">
-        <v>17.581719183715883</v>
+        <v>17.527280239724924</v>
       </c>
       <c r="R111">
-        <v>53.196775208514168</v>
+        <v>53.043150454655688</v>
       </c>
       <c r="S111" t="s">
         <v>239</v>
@@ -6227,10 +6244,10 @@
         <v>8</v>
       </c>
       <c r="Q112">
-        <v>23.0458728607606</v>
+        <v>23.129035583947079</v>
       </c>
       <c r="R112">
-        <v>52.968147537812392</v>
+        <v>53.220134909443168</v>
       </c>
       <c r="S112" t="s">
         <v>241</v>
@@ -6244,10 +6261,10 @@
         <v>8</v>
       </c>
       <c r="Q113">
-        <v>15.304593124504157</v>
+        <v>15.16673080647341</v>
       </c>
       <c r="R113">
-        <v>53.194499256083724</v>
+        <v>52.645003231161056</v>
       </c>
       <c r="S113" t="s">
         <v>243</v>
@@ -6261,10 +6278,10 @@
         <v>8</v>
       </c>
       <c r="Q114">
-        <v>16.472789268249258</v>
+        <v>16.109615043411317</v>
       </c>
       <c r="R114">
-        <v>51.400799441590003</v>
+        <v>50.927035346571493</v>
       </c>
       <c r="S114" t="s">
         <v>245</v>
@@ -6278,35 +6295,35 @@
         <v>8</v>
       </c>
       <c r="Q115">
-        <v>18.105616718911509</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R115">
-        <v>51.244509727206619</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S115" t="s">
-        <v>359</v>
+        <v>247</v>
       </c>
     </row>
     <row r="116" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O116" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P116" t="s">
         <v>8</v>
       </c>
       <c r="Q116">
-        <v>16.733772344126869</v>
+        <v>16.658975418762132</v>
       </c>
       <c r="R116">
-        <v>50.76219887306744</v>
+        <v>50.279268599866718</v>
       </c>
       <c r="S116" t="s">
-        <v>361</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O117" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="P117" t="s">
         <v>8</v>
@@ -6323,7 +6340,7 @@
     </row>
     <row r="118" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O118" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="P118" t="s">
         <v>8</v>
@@ -6332,7 +6349,7 @@
         <v>17.419694531519191</v>
       </c>
       <c r="R118">
-        <v>54.392131000242507</v>
+        <v>54.3921310002425</v>
       </c>
       <c r="S118" t="s">
         <v>253</v>
@@ -6340,16 +6357,16 @@
     </row>
     <row r="119" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O119" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="P119" t="s">
         <v>8</v>
       </c>
       <c r="Q119">
-        <v>20.492161121941823</v>
+        <v>20.6609465803446</v>
       </c>
       <c r="R119">
-        <v>53.90075879968235</v>
+        <v>54.215908666282239</v>
       </c>
       <c r="S119" t="s">
         <v>255</v>
@@ -6357,33 +6374,33 @@
     </row>
     <row r="120" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O120" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="P120" t="s">
         <v>8</v>
       </c>
       <c r="Q120">
-        <v>15.198798723531963</v>
+        <v>15.361927969342226</v>
       </c>
       <c r="R120">
-        <v>51.04618038583336</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S120" t="s">
-        <v>366</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O121" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="P121" t="s">
         <v>8</v>
       </c>
       <c r="Q121">
-        <v>18.70294226213645</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R121">
-        <v>53.953418222130388</v>
+        <v>53.942470818380237</v>
       </c>
       <c r="S121" t="s">
         <v>259</v>
@@ -6391,16 +6408,16 @@
     </row>
     <row r="122" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O122" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P122" t="s">
         <v>8</v>
       </c>
       <c r="Q122">
-        <v>21.770857300719211</v>
+        <v>21.814778267800516</v>
       </c>
       <c r="R122">
-        <v>52.911855600577397</v>
+        <v>53.031656729647359</v>
       </c>
       <c r="S122" t="s">
         <v>261</v>
@@ -6408,16 +6425,16 @@
     </row>
     <row r="123" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O123" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="P123" t="s">
         <v>8</v>
       </c>
       <c r="Q123">
-        <v>15.234781597502089</v>
+        <v>14.819703456589529</v>
       </c>
       <c r="R123">
-        <v>52.133481198606368</v>
+        <v>51.922744864982697</v>
       </c>
       <c r="S123" t="s">
         <v>263</v>
@@ -6425,16 +6442,16 @@
     </row>
     <row r="124" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O124" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="P124" t="s">
         <v>8</v>
       </c>
       <c r="Q124">
-        <v>15.361927969342224</v>
+        <v>14.904646511080676</v>
       </c>
       <c r="R124">
-        <v>53.942470818380237</v>
+        <v>53.792584091092806</v>
       </c>
       <c r="S124" t="s">
         <v>265</v>
@@ -6442,16 +6459,16 @@
     </row>
     <row r="125" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O125" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="P125" t="s">
         <v>8</v>
       </c>
       <c r="Q125">
-        <v>21.599995349696041</v>
+        <v>22.608798223120601</v>
       </c>
       <c r="R125">
-        <v>49.626238205178431</v>
+        <v>49.490542406443481</v>
       </c>
       <c r="S125" t="s">
         <v>267</v>
@@ -6459,16 +6476,16 @@
     </row>
     <row r="126" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O126" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="P126" t="s">
         <v>8</v>
       </c>
       <c r="Q126">
-        <v>22.534166549818089</v>
+        <v>22.581041961268149</v>
       </c>
       <c r="R126">
-        <v>54.009104014230232</v>
+        <v>54.334057528005133</v>
       </c>
       <c r="S126" t="s">
         <v>269</v>
@@ -6476,16 +6493,16 @@
     </row>
     <row r="127" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O127" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="P127" t="s">
         <v>8</v>
       </c>
       <c r="Q127">
-        <v>19.722955756945726</v>
+        <v>19.484239146008623</v>
       </c>
       <c r="R127">
-        <v>51.606881385274058</v>
+        <v>51.248953117858669</v>
       </c>
       <c r="S127" t="s">
         <v>271</v>
@@ -6493,7 +6510,7 @@
     </row>
     <row r="128" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O128" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="P128" t="s">
         <v>8</v>
@@ -6502,7 +6519,7 @@
         <v>18.791538906303831</v>
       </c>
       <c r="R128">
-        <v>51.607784085577883</v>
+        <v>51.694169909068883</v>
       </c>
       <c r="S128" t="s">
         <v>273</v>
@@ -6510,33 +6527,33 @@
     </row>
     <row r="129" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O129" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="P129" t="s">
         <v>8</v>
       </c>
       <c r="Q129">
-        <v>23.418504807003217</v>
+        <v>23.592994218050087</v>
       </c>
       <c r="R129">
-        <v>50.648789659390587</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S129" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
     </row>
     <row r="130" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O130" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="P130" t="s">
         <v>8</v>
       </c>
       <c r="Q130">
-        <v>16.343285359812334</v>
+        <v>16.171652634518797</v>
       </c>
       <c r="R130">
-        <v>53.711878482127347</v>
+        <v>53.832005977672566</v>
       </c>
       <c r="S130" t="s">
         <v>277</v>
@@ -6544,16 +6561,16 @@
     </row>
     <row r="131" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O131" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="P131" t="s">
         <v>8</v>
       </c>
       <c r="Q131">
-        <v>16.047850156734544</v>
+        <v>16.047850156734548</v>
       </c>
       <c r="R131">
-        <v>51.955421759583338</v>
+        <v>51.861260822850973</v>
       </c>
       <c r="S131" t="s">
         <v>279</v>
@@ -6561,409 +6578,460 @@
     </row>
     <row r="132" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O132" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="P132" t="s">
         <v>8</v>
       </c>
       <c r="Q132">
-        <v>20.849305468480804</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R132">
-        <v>49.979847832487074</v>
+        <v>49.895529181619793</v>
       </c>
       <c r="S132" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="133" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O133" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="P133" t="s">
         <v>8</v>
       </c>
       <c r="Q133">
-        <v>23.091175379404827</v>
+        <v>20.8493054684808</v>
       </c>
       <c r="R133">
-        <v>51.490170313293042</v>
+        <v>49.91077177331681</v>
       </c>
       <c r="S133" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="134" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O134" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="P134" t="s">
         <v>8</v>
       </c>
       <c r="Q134">
-        <v>22.221149843265444</v>
+        <v>23.508838878966412</v>
       </c>
       <c r="R134">
-        <v>49.895529181619793</v>
+        <v>51.694088645539807</v>
       </c>
       <c r="S134" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="135" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O135" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="P135" t="s">
         <v>8</v>
       </c>
       <c r="Q135">
-        <v>20.723463068828806</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R135">
-        <v>51.206608290896526</v>
+        <v>49.895529181619793</v>
       </c>
       <c r="S135" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="136" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O136" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="P136" t="s">
         <v>8</v>
       </c>
       <c r="Q136">
-        <v>21.535227655873118</v>
+        <v>20.409532233050189</v>
       </c>
       <c r="R136">
-        <v>50.345189363482064</v>
+        <v>50.93087347353012</v>
       </c>
       <c r="S136" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="137" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O137" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="P137" t="s">
         <v>8</v>
       </c>
       <c r="Q137">
-        <v>22.221149843265444</v>
+        <v>21.535227655873118</v>
       </c>
       <c r="R137">
-        <v>50.702019523773188</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S137" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="138" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O138" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="P138" t="s">
         <v>8</v>
       </c>
       <c r="Q138">
-        <v>19.141537976370479</v>
+        <v>22.221149843265444</v>
       </c>
       <c r="R138">
-        <v>50.794849545344341</v>
+        <v>50.408257221982232</v>
       </c>
       <c r="S138" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="139" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O139" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="P139" t="s">
         <v>8</v>
       </c>
       <c r="Q139">
-        <v>18.791538906303831</v>
+        <v>19.266410025240862</v>
       </c>
       <c r="R139">
-        <v>52.866942494850733</v>
+        <v>50.794849545344334</v>
       </c>
       <c r="S139" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="140" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O140" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="P140" t="s">
         <v>8</v>
       </c>
       <c r="Q140">
-        <v>21.535227655873118</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R140">
-        <v>51.12207241004873</v>
+        <v>53.043150454655681</v>
       </c>
       <c r="S140" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="141" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O141" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="P141" t="s">
         <v>8</v>
       </c>
       <c r="Q141">
-        <v>18.443463902914296</v>
+        <v>21.535227655873118</v>
       </c>
       <c r="R141">
-        <v>52.152617042117903</v>
+        <v>50.888635183462817</v>
       </c>
       <c r="S141" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="142" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O142" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="P142" t="s">
         <v>8</v>
       </c>
       <c r="Q142">
-        <v>16.733772344126869</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R142">
-        <v>54.3921310002425</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S142" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="143" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O143" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="P143" t="s">
         <v>8</v>
       </c>
       <c r="Q143">
-        <v>21.004381926924367</v>
+        <v>18.41752059971844</v>
       </c>
       <c r="R143">
-        <v>52.40875253328344</v>
+        <v>52.143830090931147</v>
       </c>
       <c r="S143" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="144" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O144" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="P144" t="s">
         <v>8</v>
       </c>
       <c r="Q144">
-        <v>18.791538906303831</v>
+        <v>16.733772344126869</v>
       </c>
       <c r="R144">
-        <v>50.345189363482064</v>
+        <v>54.3921310002425</v>
       </c>
       <c r="S144" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="145" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O145" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="P145" t="s">
         <v>8</v>
       </c>
       <c r="Q145">
-        <v>21.839359413405159</v>
+        <v>21.182327215095697</v>
       </c>
       <c r="R145">
-        <v>53.798677421956477</v>
+        <v>52.208865366630896</v>
       </c>
       <c r="S145" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="146" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O146" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="P146" t="s">
         <v>8</v>
       </c>
       <c r="Q146">
-        <v>16.811054032011597</v>
+        <v>18.791538906303831</v>
       </c>
       <c r="R146">
-        <v>52.578511324728609</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S146" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="147" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O147" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="P147" t="s">
         <v>8</v>
       </c>
       <c r="Q147">
-        <v>18.105616718911509</v>
+        <v>21.703352022374737</v>
       </c>
       <c r="R147">
-        <v>50.345189363482064</v>
+        <v>54.13287173739576</v>
       </c>
       <c r="S147" t="s">
-        <v>395</v>
+        <v>311</v>
       </c>
     </row>
     <row r="148" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O148" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="P148" t="s">
         <v>8</v>
       </c>
       <c r="Q148">
-        <v>14.6760057819499</v>
+        <v>16.588549565253906</v>
       </c>
       <c r="R148">
-        <v>53.043150454655688</v>
+        <v>53.010781572357352</v>
       </c>
       <c r="S148" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="149" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O149" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="P149" t="s">
         <v>8</v>
       </c>
       <c r="Q149">
-        <v>19.477461093696157</v>
+        <v>18.105616718911509</v>
       </c>
       <c r="R149">
         <v>50.345189363482064</v>
       </c>
       <c r="S149" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="150" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O150" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="P150" t="s">
         <v>8</v>
       </c>
       <c r="Q150">
-        <v>19.306038498498257</v>
+        <v>14.676005781949904</v>
       </c>
       <c r="R150">
-        <v>53.830093763447763</v>
+        <v>53.043150454655688</v>
       </c>
       <c r="S150" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="151" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O151" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="P151" t="s">
         <v>8</v>
       </c>
       <c r="Q151">
-        <v>19.902988727679805</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R151">
-        <v>52.628323275925922</v>
+        <v>50.345189363482064</v>
       </c>
       <c r="S151" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="152" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O152" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="P152" t="s">
         <v>8</v>
       </c>
       <c r="Q152">
-        <v>17.419694531519191</v>
+        <v>19.403780261531288</v>
       </c>
       <c r="R152">
-        <v>51.615078540529446</v>
+        <v>49.674521586203319</v>
       </c>
       <c r="S152" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="153" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O153" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="P153" t="s">
         <v>8</v>
       </c>
       <c r="Q153">
-        <v>18.105616718911509</v>
+        <v>19.477461093696157</v>
       </c>
       <c r="R153">
-        <v>54.392131000242507</v>
+        <v>53.942470818380237</v>
       </c>
       <c r="S153" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="154" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O154" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="P154" t="s">
         <v>8</v>
       </c>
       <c r="Q154">
-        <v>20.163383281088478</v>
+        <v>19.869295209633083</v>
       </c>
       <c r="R154">
-        <v>50.345189363482064</v>
+        <v>52.66680063954901</v>
       </c>
       <c r="S154" t="s">
-        <v>403</v>
+        <v>325</v>
       </c>
     </row>
     <row r="155" spans="15:19" x14ac:dyDescent="0.45">
       <c r="O155" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="P155" t="s">
         <v>8</v>
       </c>
       <c r="Q155">
-        <v>22.194399267951567</v>
+        <v>17.419694531519191</v>
       </c>
       <c r="R155">
-        <v>51.821273485020299</v>
+        <v>51.244509727206612</v>
       </c>
       <c r="S155" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="156" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O156" t="s">
+        <v>399</v>
+      </c>
+      <c r="P156" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q156">
+        <v>18.105616718911509</v>
+      </c>
+      <c r="R156">
+        <v>54.3921310002425</v>
+      </c>
+      <c r="S156" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="157" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O157" t="s">
+        <v>400</v>
+      </c>
+      <c r="P157" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q157">
+        <v>20.163383281088478</v>
+      </c>
+      <c r="R157">
+        <v>49.63609311948067</v>
+      </c>
+      <c r="S157" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="158" spans="15:19" x14ac:dyDescent="0.45">
+      <c r="O158" t="s">
+        <v>401</v>
+      </c>
+      <c r="P158" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q158">
+        <v>22.196099857010601</v>
+      </c>
+      <c r="R158">
+        <v>51.918163705689693</v>
+      </c>
+      <c r="S158" t="s">
         <v>333</v>
       </c>
     </row>
@@ -6973,19 +7041,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{498974E5-2C79-4E7B-8BC8-95C6C5774924}">
-  <dimension ref="B3:L62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A3B452-5E97-43B7-97F8-488823139CF2}">
+  <dimension ref="B3:S82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="K3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -7013,8 +7084,23 @@
       <c r="L4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="O4" t="s">
+        <v>233</v>
+      </c>
+      <c r="P4" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>235</v>
+      </c>
+      <c r="R4" t="s">
+        <v>236</v>
+      </c>
+      <c r="S4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -7022,1678 +7108,2654 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E5" t="s">
+        <v>403</v>
+      </c>
+      <c r="F5" t="s">
+        <v>404</v>
+      </c>
+      <c r="G5" t="s">
         <v>405</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>406</v>
       </c>
-      <c r="F5" t="s">
+      <c r="K5" t="s">
+        <v>405</v>
+      </c>
+      <c r="L5" t="s">
+        <v>540</v>
+      </c>
+      <c r="O5" t="s">
         <v>407</v>
       </c>
-      <c r="G5" t="s">
+      <c r="P5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5">
+        <v>22.9435906</v>
+      </c>
+      <c r="R5">
+        <v>52.934591495109792</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>402</v>
+      </c>
+      <c r="E6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F6" t="s">
         <v>408</v>
       </c>
-      <c r="H5" t="s">
+      <c r="G6" t="s">
         <v>409</v>
       </c>
-      <c r="K5" t="s">
+      <c r="H6" t="s">
+        <v>406</v>
+      </c>
+      <c r="K6" t="s">
+        <v>409</v>
+      </c>
+      <c r="L6" t="s">
+        <v>541</v>
+      </c>
+      <c r="O6" t="s">
+        <v>503</v>
+      </c>
+      <c r="P6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q6">
+        <v>19.212740275249061</v>
+      </c>
+      <c r="R6">
+        <v>49.84240724566758</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F7" t="s">
+        <v>411</v>
+      </c>
+      <c r="G7" t="s">
+        <v>412</v>
+      </c>
+      <c r="H7" t="s">
+        <v>406</v>
+      </c>
+      <c r="K7" t="s">
+        <v>412</v>
+      </c>
+      <c r="L7" t="s">
+        <v>542</v>
+      </c>
+      <c r="O7" t="s">
+        <v>430</v>
+      </c>
+      <c r="P7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7">
+        <v>15.114048637999945</v>
+      </c>
+      <c r="R7">
+        <v>51.092587962369954</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>402</v>
+      </c>
+      <c r="E8" t="s">
+        <v>413</v>
+      </c>
+      <c r="F8" t="s">
+        <v>414</v>
+      </c>
+      <c r="G8" t="s">
+        <v>415</v>
+      </c>
+      <c r="H8" t="s">
+        <v>406</v>
+      </c>
+      <c r="K8" t="s">
+        <v>415</v>
+      </c>
+      <c r="L8" t="s">
+        <v>543</v>
+      </c>
+      <c r="O8" t="s">
+        <v>403</v>
+      </c>
+      <c r="P8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8">
+        <v>18.136420151493411</v>
+      </c>
+      <c r="R8">
+        <v>53.09476020715347</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E9" t="s">
+        <v>416</v>
+      </c>
+      <c r="F9" t="s">
+        <v>417</v>
+      </c>
+      <c r="G9" t="s">
+        <v>418</v>
+      </c>
+      <c r="H9" t="s">
+        <v>406</v>
+      </c>
+      <c r="K9" t="s">
+        <v>418</v>
+      </c>
+      <c r="L9" t="s">
+        <v>544</v>
+      </c>
+      <c r="O9" t="s">
+        <v>464</v>
+      </c>
+      <c r="P9" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9">
+        <v>23.439530165761369</v>
+      </c>
+      <c r="R9">
+        <v>51.15840073090456</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>402</v>
+      </c>
+      <c r="E10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F10" t="s">
+        <v>420</v>
+      </c>
+      <c r="G10" t="s">
+        <v>421</v>
+      </c>
+      <c r="H10" t="s">
+        <v>406</v>
+      </c>
+      <c r="K10" t="s">
+        <v>421</v>
+      </c>
+      <c r="L10" t="s">
+        <v>545</v>
+      </c>
+      <c r="O10" t="s">
+        <v>474</v>
+      </c>
+      <c r="P10" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10">
+        <v>19.142315791015029</v>
+      </c>
+      <c r="R10">
+        <v>50.832052960395522</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>402</v>
+      </c>
+      <c r="E11" t="s">
+        <v>422</v>
+      </c>
+      <c r="F11" t="s">
+        <v>404</v>
+      </c>
+      <c r="G11" t="s">
+        <v>423</v>
+      </c>
+      <c r="H11" t="s">
+        <v>406</v>
+      </c>
+      <c r="K11" t="s">
+        <v>423</v>
+      </c>
+      <c r="L11" t="s">
+        <v>546</v>
+      </c>
+      <c r="O11" t="s">
+        <v>466</v>
+      </c>
+      <c r="P11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11">
+        <v>21.932877434209747</v>
+      </c>
+      <c r="R11">
+        <v>49.994080927127975</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>402</v>
+      </c>
+      <c r="E12" t="s">
+        <v>424</v>
+      </c>
+      <c r="F12" t="s">
+        <v>425</v>
+      </c>
+      <c r="G12" t="s">
+        <v>426</v>
+      </c>
+      <c r="H12" t="s">
+        <v>406</v>
+      </c>
+      <c r="K12" t="s">
+        <v>426</v>
+      </c>
+      <c r="L12" t="s">
+        <v>547</v>
+      </c>
+      <c r="O12" t="s">
+        <v>492</v>
+      </c>
+      <c r="P12" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12">
+        <v>22.30185788377095</v>
+      </c>
+      <c r="R12">
+        <v>53.757586946292747</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>402</v>
+      </c>
+      <c r="E13" t="s">
+        <v>427</v>
+      </c>
+      <c r="F13" t="s">
+        <v>428</v>
+      </c>
+      <c r="G13" t="s">
+        <v>429</v>
+      </c>
+      <c r="H13" t="s">
+        <v>406</v>
+      </c>
+      <c r="K13" t="s">
+        <v>429</v>
+      </c>
+      <c r="L13" t="s">
+        <v>548</v>
+      </c>
+      <c r="O13" t="s">
+        <v>432</v>
+      </c>
+      <c r="P13" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13">
+        <v>18.709473829191406</v>
+      </c>
+      <c r="R13">
+        <v>54.338650185173492</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>402</v>
+      </c>
+      <c r="E14" t="s">
+        <v>430</v>
+      </c>
+      <c r="F14" t="s">
+        <v>414</v>
+      </c>
+      <c r="G14" t="s">
+        <v>431</v>
+      </c>
+      <c r="H14" t="s">
+        <v>406</v>
+      </c>
+      <c r="K14" t="s">
+        <v>431</v>
+      </c>
+      <c r="L14" t="s">
+        <v>549</v>
+      </c>
+      <c r="O14" t="s">
+        <v>513</v>
+      </c>
+      <c r="P14" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14">
+        <v>18.109334026299528</v>
+      </c>
+      <c r="R14">
+        <v>54.718832956325642</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>402</v>
+      </c>
+      <c r="E15" t="s">
+        <v>432</v>
+      </c>
+      <c r="F15" t="s">
+        <v>428</v>
+      </c>
+      <c r="G15" t="s">
+        <v>433</v>
+      </c>
+      <c r="H15" t="s">
+        <v>406</v>
+      </c>
+      <c r="K15" t="s">
+        <v>433</v>
+      </c>
+      <c r="L15" t="s">
+        <v>550</v>
+      </c>
+      <c r="O15" t="s">
+        <v>490</v>
+      </c>
+      <c r="P15" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15">
+        <v>18.772002420791907</v>
+      </c>
+      <c r="R15">
+        <v>50.365380141626972</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>402</v>
+      </c>
+      <c r="E16" t="s">
+        <v>434</v>
+      </c>
+      <c r="F16" t="s">
         <v>408</v>
       </c>
-      <c r="L5" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>405</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="G16" t="s">
+        <v>435</v>
+      </c>
+      <c r="H16" t="s">
+        <v>406</v>
+      </c>
+      <c r="K16" t="s">
+        <v>435</v>
+      </c>
+      <c r="L16" t="s">
+        <v>551</v>
+      </c>
+      <c r="O16" t="s">
         <v>410</v>
       </c>
-      <c r="F6" t="s">
+      <c r="P16" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16">
+        <v>15.036772099999991</v>
+      </c>
+      <c r="R16">
+        <v>52.764178895043841</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>402</v>
+      </c>
+      <c r="E17" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" t="s">
+        <v>414</v>
+      </c>
+      <c r="G17" t="s">
+        <v>437</v>
+      </c>
+      <c r="H17" t="s">
+        <v>406</v>
+      </c>
+      <c r="K17" t="s">
+        <v>437</v>
+      </c>
+      <c r="L17" t="s">
+        <v>552</v>
+      </c>
+      <c r="O17" t="s">
+        <v>444</v>
+      </c>
+      <c r="P17" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17">
+        <v>22.32320624934065</v>
+      </c>
+      <c r="R17">
+        <v>53.773833315299122</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E18" t="s">
+        <v>438</v>
+      </c>
+      <c r="F18" t="s">
+        <v>439</v>
+      </c>
+      <c r="G18" t="s">
+        <v>440</v>
+      </c>
+      <c r="H18" t="s">
+        <v>406</v>
+      </c>
+      <c r="K18" t="s">
+        <v>440</v>
+      </c>
+      <c r="L18" t="s">
+        <v>553</v>
+      </c>
+      <c r="O18" t="s">
+        <v>505</v>
+      </c>
+      <c r="P18" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18">
+        <v>18.80413943487487</v>
+      </c>
+      <c r="R18">
+        <v>53.446973465922014</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>402</v>
+      </c>
+      <c r="E19" t="s">
+        <v>441</v>
+      </c>
+      <c r="F19" t="s">
+        <v>442</v>
+      </c>
+      <c r="G19" t="s">
+        <v>443</v>
+      </c>
+      <c r="H19" t="s">
+        <v>406</v>
+      </c>
+      <c r="K19" t="s">
+        <v>443</v>
+      </c>
+      <c r="L19" t="s">
+        <v>554</v>
+      </c>
+      <c r="O19" t="s">
+        <v>501</v>
+      </c>
+      <c r="P19" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19">
+        <v>19.26958678998464</v>
+      </c>
+      <c r="R19">
+        <v>50.325695616526026</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>402</v>
+      </c>
+      <c r="E20" t="s">
+        <v>444</v>
+      </c>
+      <c r="F20" t="s">
+        <v>428</v>
+      </c>
+      <c r="G20" t="s">
+        <v>445</v>
+      </c>
+      <c r="H20" t="s">
+        <v>406</v>
+      </c>
+      <c r="K20" t="s">
+        <v>445</v>
+      </c>
+      <c r="L20" t="s">
+        <v>555</v>
+      </c>
+      <c r="O20" t="s">
+        <v>497</v>
+      </c>
+      <c r="P20" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20">
+        <v>17.971461740692011</v>
+      </c>
+      <c r="R20">
+        <v>50.613417792273673</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>402</v>
+      </c>
+      <c r="E21" t="s">
+        <v>446</v>
+      </c>
+      <c r="F21" t="s">
+        <v>447</v>
+      </c>
+      <c r="G21" t="s">
+        <v>448</v>
+      </c>
+      <c r="H21" t="s">
+        <v>406</v>
+      </c>
+      <c r="K21" t="s">
+        <v>448</v>
+      </c>
+      <c r="L21" t="s">
+        <v>556</v>
+      </c>
+      <c r="O21" t="s">
+        <v>468</v>
+      </c>
+      <c r="P21" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21">
+        <v>20.414702726123267</v>
+      </c>
+      <c r="R21">
+        <v>50.89970891903441</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>402</v>
+      </c>
+      <c r="E22" t="s">
+        <v>449</v>
+      </c>
+      <c r="F22" t="s">
+        <v>450</v>
+      </c>
+      <c r="G22" t="s">
+        <v>451</v>
+      </c>
+      <c r="H22" t="s">
+        <v>406</v>
+      </c>
+      <c r="K22" t="s">
+        <v>451</v>
+      </c>
+      <c r="L22" t="s">
+        <v>557</v>
+      </c>
+      <c r="O22" t="s">
+        <v>483</v>
+      </c>
+      <c r="P22" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22">
+        <v>18.23382697092811</v>
+      </c>
+      <c r="R22">
+        <v>52.305225562416602</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>402</v>
+      </c>
+      <c r="E23" t="s">
+        <v>452</v>
+      </c>
+      <c r="F23" t="s">
+        <v>442</v>
+      </c>
+      <c r="G23" t="s">
+        <v>453</v>
+      </c>
+      <c r="H23" t="s">
+        <v>406</v>
+      </c>
+      <c r="K23" t="s">
+        <v>453</v>
+      </c>
+      <c r="L23" t="s">
+        <v>558</v>
+      </c>
+      <c r="O23" t="s">
+        <v>454</v>
+      </c>
+      <c r="P23" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23">
+        <v>16.710076017737201</v>
+      </c>
+      <c r="R23">
+        <v>54.024054311061576</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>402</v>
+      </c>
+      <c r="E24" t="s">
+        <v>454</v>
+      </c>
+      <c r="F24" t="s">
+        <v>455</v>
+      </c>
+      <c r="G24" t="s">
+        <v>456</v>
+      </c>
+      <c r="H24" t="s">
+        <v>406</v>
+      </c>
+      <c r="K24" t="s">
+        <v>456</v>
+      </c>
+      <c r="L24" t="s">
+        <v>559</v>
+      </c>
+      <c r="O24" t="s">
+        <v>516</v>
+      </c>
+      <c r="P24" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24">
+        <v>20.098449471876847</v>
+      </c>
+      <c r="R24">
+        <v>50.096013088752883</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>402</v>
+      </c>
+      <c r="E25" t="s">
+        <v>457</v>
+      </c>
+      <c r="F25" t="s">
+        <v>414</v>
+      </c>
+      <c r="G25" t="s">
+        <v>458</v>
+      </c>
+      <c r="H25" t="s">
+        <v>406</v>
+      </c>
+      <c r="K25" t="s">
+        <v>458</v>
+      </c>
+      <c r="L25" t="s">
+        <v>560</v>
+      </c>
+      <c r="O25" t="s">
+        <v>441</v>
+      </c>
+      <c r="P25" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25">
+        <v>21.852623292646182</v>
+      </c>
+      <c r="R25">
+        <v>49.688226064614483</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" t="s">
+        <v>459</v>
+      </c>
+      <c r="F26" t="s">
+        <v>460</v>
+      </c>
+      <c r="G26" t="s">
+        <v>461</v>
+      </c>
+      <c r="H26" t="s">
+        <v>406</v>
+      </c>
+      <c r="K26" t="s">
+        <v>461</v>
+      </c>
+      <c r="L26" t="s">
+        <v>561</v>
+      </c>
+      <c r="O26" t="s">
+        <v>422</v>
+      </c>
+      <c r="P26" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26">
+        <v>18.807259299999998</v>
+      </c>
+      <c r="R26">
+        <v>53.420298595291477</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E27" t="s">
+        <v>462</v>
+      </c>
+      <c r="F27" t="s">
+        <v>460</v>
+      </c>
+      <c r="G27" t="s">
+        <v>463</v>
+      </c>
+      <c r="H27" t="s">
+        <v>406</v>
+      </c>
+      <c r="K27" t="s">
+        <v>463</v>
+      </c>
+      <c r="L27" t="s">
+        <v>562</v>
+      </c>
+      <c r="O27" t="s">
+        <v>413</v>
+      </c>
+      <c r="P27" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27">
+        <v>16.425764160923386</v>
+      </c>
+      <c r="R27">
+        <v>51.187765701036277</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" t="s">
+        <v>402</v>
+      </c>
+      <c r="E28" t="s">
+        <v>464</v>
+      </c>
+      <c r="F28" t="s">
+        <v>442</v>
+      </c>
+      <c r="G28" t="s">
+        <v>465</v>
+      </c>
+      <c r="H28" t="s">
+        <v>406</v>
+      </c>
+      <c r="K28" t="s">
+        <v>465</v>
+      </c>
+      <c r="L28" t="s">
+        <v>563</v>
+      </c>
+      <c r="O28" t="s">
+        <v>434</v>
+      </c>
+      <c r="P28" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28">
+        <v>21.622064197413163</v>
+      </c>
+      <c r="R28">
+        <v>53.106985778887129</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>402</v>
+      </c>
+      <c r="E29" t="s">
+        <v>466</v>
+      </c>
+      <c r="F29" t="s">
+        <v>442</v>
+      </c>
+      <c r="G29" t="s">
+        <v>467</v>
+      </c>
+      <c r="H29" t="s">
+        <v>406</v>
+      </c>
+      <c r="K29" t="s">
+        <v>467</v>
+      </c>
+      <c r="L29" t="s">
+        <v>564</v>
+      </c>
+      <c r="O29" t="s">
+        <v>457</v>
+      </c>
+      <c r="P29" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29">
+        <v>16.005965049711531</v>
+      </c>
+      <c r="R29">
+        <v>51.662137784346321</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>402</v>
+      </c>
+      <c r="E30" t="s">
+        <v>468</v>
+      </c>
+      <c r="F30" t="s">
+        <v>447</v>
+      </c>
+      <c r="G30" t="s">
+        <v>469</v>
+      </c>
+      <c r="H30" t="s">
+        <v>406</v>
+      </c>
+      <c r="K30" t="s">
+        <v>469</v>
+      </c>
+      <c r="L30" t="s">
+        <v>565</v>
+      </c>
+      <c r="O30" t="s">
+        <v>470</v>
+      </c>
+      <c r="P30" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q30">
+        <v>21.329216800872093</v>
+      </c>
+      <c r="R30">
+        <v>50.441384740226297</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>402</v>
+      </c>
+      <c r="E31" t="s">
+        <v>470</v>
+      </c>
+      <c r="F31" t="s">
+        <v>442</v>
+      </c>
+      <c r="G31" t="s">
+        <v>471</v>
+      </c>
+      <c r="H31" t="s">
+        <v>406</v>
+      </c>
+      <c r="K31" t="s">
+        <v>471</v>
+      </c>
+      <c r="L31" t="s">
+        <v>566</v>
+      </c>
+      <c r="O31" t="s">
+        <v>416</v>
+      </c>
+      <c r="P31" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q31">
+        <v>17.694280600000003</v>
+      </c>
+      <c r="R31">
+        <v>51.108497194339172</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>402</v>
+      </c>
+      <c r="E32" t="s">
+        <v>472</v>
+      </c>
+      <c r="F32" t="s">
+        <v>442</v>
+      </c>
+      <c r="G32" t="s">
+        <v>473</v>
+      </c>
+      <c r="H32" t="s">
+        <v>406</v>
+      </c>
+      <c r="K32" t="s">
+        <v>473</v>
+      </c>
+      <c r="L32" t="s">
+        <v>567</v>
+      </c>
+      <c r="O32" t="s">
+        <v>427</v>
+      </c>
+      <c r="P32" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32">
+        <v>20.529140970063281</v>
+      </c>
+      <c r="R32">
+        <v>53.802992196846674</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>402</v>
+      </c>
+      <c r="E33" t="s">
+        <v>474</v>
+      </c>
+      <c r="F33" t="s">
+        <v>450</v>
+      </c>
+      <c r="G33" t="s">
+        <v>475</v>
+      </c>
+      <c r="H33" t="s">
+        <v>406</v>
+      </c>
+      <c r="K33" t="s">
+        <v>475</v>
+      </c>
+      <c r="L33" t="s">
+        <v>568</v>
+      </c>
+      <c r="O33" t="s">
+        <v>481</v>
+      </c>
+      <c r="P33" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33">
+        <v>17.872695321486159</v>
+      </c>
+      <c r="R33">
+        <v>50.746544696597532</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
+        <v>402</v>
+      </c>
+      <c r="E34" t="s">
+        <v>476</v>
+      </c>
+      <c r="F34" t="s">
+        <v>477</v>
+      </c>
+      <c r="G34" t="s">
+        <v>478</v>
+      </c>
+      <c r="H34" t="s">
+        <v>406</v>
+      </c>
+      <c r="K34" t="s">
+        <v>478</v>
+      </c>
+      <c r="L34" t="s">
+        <v>569</v>
+      </c>
+      <c r="O34" t="s">
+        <v>479</v>
+      </c>
+      <c r="P34" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q34">
+        <v>21.451867596848331</v>
+      </c>
+      <c r="R34">
+        <v>50.938934166502882</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>402</v>
+      </c>
+      <c r="E35" t="s">
+        <v>479</v>
+      </c>
+      <c r="F35" t="s">
+        <v>442</v>
+      </c>
+      <c r="G35" t="s">
+        <v>480</v>
+      </c>
+      <c r="H35" t="s">
+        <v>406</v>
+      </c>
+      <c r="K35" t="s">
+        <v>480</v>
+      </c>
+      <c r="L35" t="s">
+        <v>570</v>
+      </c>
+      <c r="O35" t="s">
+        <v>446</v>
+      </c>
+      <c r="P35" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>19.683344241421601</v>
+      </c>
+      <c r="R35">
+        <v>51.428225694344057</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>402</v>
+      </c>
+      <c r="E36" t="s">
+        <v>481</v>
+      </c>
+      <c r="F36" t="s">
+        <v>417</v>
+      </c>
+      <c r="G36" t="s">
+        <v>482</v>
+      </c>
+      <c r="H36" t="s">
+        <v>406</v>
+      </c>
+      <c r="K36" t="s">
+        <v>482</v>
+      </c>
+      <c r="L36" t="s">
+        <v>571</v>
+      </c>
+      <c r="O36" t="s">
+        <v>507</v>
+      </c>
+      <c r="P36" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q36">
+        <v>19.702975226287894</v>
+      </c>
+      <c r="R36">
+        <v>52.585421539045129</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>402</v>
+      </c>
+      <c r="E37" t="s">
+        <v>483</v>
+      </c>
+      <c r="F37" t="s">
+        <v>484</v>
+      </c>
+      <c r="G37" t="s">
+        <v>485</v>
+      </c>
+      <c r="H37" t="s">
+        <v>406</v>
+      </c>
+      <c r="K37" t="s">
+        <v>485</v>
+      </c>
+      <c r="L37" t="s">
+        <v>572</v>
+      </c>
+      <c r="O37" t="s">
+        <v>438</v>
+      </c>
+      <c r="P37" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q37">
+        <v>14.521960541156195</v>
+      </c>
+      <c r="R37">
+        <v>53.564351149135263</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>402</v>
+      </c>
+      <c r="E38" t="s">
+        <v>486</v>
+      </c>
+      <c r="F38" t="s">
+        <v>425</v>
+      </c>
+      <c r="G38" t="s">
+        <v>487</v>
+      </c>
+      <c r="H38" t="s">
+        <v>406</v>
+      </c>
+      <c r="K38" t="s">
+        <v>487</v>
+      </c>
+      <c r="L38" t="s">
+        <v>573</v>
+      </c>
+      <c r="O38" t="s">
+        <v>494</v>
+      </c>
+      <c r="P38" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q38">
+        <v>16.779042268819836</v>
+      </c>
+      <c r="R38">
+        <v>52.367785611218373</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" t="s">
+        <v>402</v>
+      </c>
+      <c r="E39" t="s">
+        <v>488</v>
+      </c>
+      <c r="F39" t="s">
+        <v>442</v>
+      </c>
+      <c r="G39" t="s">
+        <v>489</v>
+      </c>
+      <c r="H39" t="s">
+        <v>406</v>
+      </c>
+      <c r="K39" t="s">
+        <v>489</v>
+      </c>
+      <c r="L39" t="s">
+        <v>574</v>
+      </c>
+      <c r="O39" t="s">
+        <v>518</v>
+      </c>
+      <c r="P39" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39">
+        <v>21.989289035599807</v>
+      </c>
+      <c r="R39">
+        <v>51.453800109559978</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>402</v>
+      </c>
+      <c r="E40" t="s">
+        <v>490</v>
+      </c>
+      <c r="F40" t="s">
+        <v>460</v>
+      </c>
+      <c r="G40" t="s">
+        <v>491</v>
+      </c>
+      <c r="H40" t="s">
+        <v>406</v>
+      </c>
+      <c r="K40" t="s">
+        <v>491</v>
+      </c>
+      <c r="L40" t="s">
+        <v>575</v>
+      </c>
+      <c r="O40" t="s">
+        <v>449</v>
+      </c>
+      <c r="P40" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q40">
+        <v>18.907832339956155</v>
+      </c>
+      <c r="R40">
+        <v>51.14274257049226</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>402</v>
+      </c>
+      <c r="E41" t="s">
+        <v>492</v>
+      </c>
+      <c r="F41" t="s">
+        <v>428</v>
+      </c>
+      <c r="G41" t="s">
+        <v>493</v>
+      </c>
+      <c r="H41" t="s">
+        <v>406</v>
+      </c>
+      <c r="K41" t="s">
+        <v>493</v>
+      </c>
+      <c r="L41" t="s">
+        <v>576</v>
+      </c>
+      <c r="O41" t="s">
+        <v>472</v>
+      </c>
+      <c r="P41" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41">
+        <v>21.87079962455832</v>
+      </c>
+      <c r="R41">
+        <v>50.190926527507919</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>402</v>
+      </c>
+      <c r="E42" t="s">
+        <v>494</v>
+      </c>
+      <c r="F42" t="s">
+        <v>495</v>
+      </c>
+      <c r="G42" t="s">
+        <v>496</v>
+      </c>
+      <c r="H42" t="s">
+        <v>406</v>
+      </c>
+      <c r="K42" t="s">
+        <v>496</v>
+      </c>
+      <c r="L42" t="s">
+        <v>577</v>
+      </c>
+      <c r="O42" t="s">
+        <v>424</v>
+      </c>
+      <c r="P42" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42">
+        <v>16.891209385550301</v>
+      </c>
+      <c r="R42">
+        <v>54.501380892532538</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>402</v>
+      </c>
+      <c r="E43" t="s">
+        <v>497</v>
+      </c>
+      <c r="F43" t="s">
+        <v>460</v>
+      </c>
+      <c r="G43" t="s">
+        <v>498</v>
+      </c>
+      <c r="H43" t="s">
+        <v>406</v>
+      </c>
+      <c r="K43" t="s">
+        <v>498</v>
+      </c>
+      <c r="L43" t="s">
+        <v>578</v>
+      </c>
+      <c r="O43" t="s">
+        <v>459</v>
+      </c>
+      <c r="P43" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43">
+        <v>18.849567300984408</v>
+      </c>
+      <c r="R43">
+        <v>50.130601442155474</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>402</v>
+      </c>
+      <c r="E44" t="s">
+        <v>499</v>
+      </c>
+      <c r="F44" t="s">
+        <v>439</v>
+      </c>
+      <c r="G44" t="s">
+        <v>500</v>
+      </c>
+      <c r="H44" t="s">
+        <v>406</v>
+      </c>
+      <c r="K44" t="s">
+        <v>500</v>
+      </c>
+      <c r="L44" t="s">
+        <v>579</v>
+      </c>
+      <c r="O44" t="s">
+        <v>419</v>
+      </c>
+      <c r="P44" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44">
+        <v>16.803664099999992</v>
+      </c>
+      <c r="R44">
+        <v>50.605684994101473</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>402</v>
+      </c>
+      <c r="E45" t="s">
+        <v>501</v>
+      </c>
+      <c r="F45" t="s">
+        <v>460</v>
+      </c>
+      <c r="G45" t="s">
+        <v>502</v>
+      </c>
+      <c r="H45" t="s">
+        <v>406</v>
+      </c>
+      <c r="K45" t="s">
+        <v>502</v>
+      </c>
+      <c r="L45" t="s">
+        <v>580</v>
+      </c>
+      <c r="O45" t="s">
+        <v>499</v>
+      </c>
+      <c r="P45" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45">
+        <v>14.476073038134764</v>
+      </c>
+      <c r="R45">
+        <v>53.19612477284646</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>402</v>
+      </c>
+      <c r="E46" t="s">
+        <v>503</v>
+      </c>
+      <c r="F46" t="s">
+        <v>460</v>
+      </c>
+      <c r="G46" t="s">
+        <v>504</v>
+      </c>
+      <c r="H46" t="s">
+        <v>406</v>
+      </c>
+      <c r="K46" t="s">
+        <v>504</v>
+      </c>
+      <c r="L46" t="s">
+        <v>581</v>
+      </c>
+      <c r="O46" t="s">
+        <v>462</v>
+      </c>
+      <c r="P46" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46">
+        <v>20.926415095548208</v>
+      </c>
+      <c r="R46">
+        <v>50.022590448951917</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>402</v>
+      </c>
+      <c r="E47" t="s">
+        <v>505</v>
+      </c>
+      <c r="F47" t="s">
+        <v>404</v>
+      </c>
+      <c r="G47" t="s">
+        <v>506</v>
+      </c>
+      <c r="H47" t="s">
+        <v>406</v>
+      </c>
+      <c r="K47" t="s">
+        <v>506</v>
+      </c>
+      <c r="L47" t="s">
+        <v>582</v>
+      </c>
+      <c r="O47" t="s">
+        <v>486</v>
+      </c>
+      <c r="P47" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47">
+        <v>16.89038355962467</v>
+      </c>
+      <c r="R47">
+        <v>54.50215260847132</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>402</v>
+      </c>
+      <c r="E48" t="s">
+        <v>507</v>
+      </c>
+      <c r="F48" t="s">
+        <v>508</v>
+      </c>
+      <c r="G48" t="s">
+        <v>509</v>
+      </c>
+      <c r="H48" t="s">
+        <v>406</v>
+      </c>
+      <c r="K48" t="s">
+        <v>509</v>
+      </c>
+      <c r="L48" t="s">
+        <v>583</v>
+      </c>
+      <c r="O48" t="s">
+        <v>488</v>
+      </c>
+      <c r="P48" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48">
+        <v>20.877296701170323</v>
+      </c>
+      <c r="R48">
+        <v>52.214439540966467</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>402</v>
+      </c>
+      <c r="E49" t="s">
+        <v>510</v>
+      </c>
+      <c r="F49" t="s">
+        <v>511</v>
+      </c>
+      <c r="G49" t="s">
+        <v>512</v>
+      </c>
+      <c r="H49" t="s">
+        <v>406</v>
+      </c>
+      <c r="K49" t="s">
+        <v>512</v>
+      </c>
+      <c r="L49" t="s">
+        <v>584</v>
+      </c>
+      <c r="O49" t="s">
+        <v>476</v>
+      </c>
+      <c r="P49" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49">
+        <v>18.956064538096921</v>
+      </c>
+      <c r="R49">
+        <v>52.714665383017554</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" t="s">
+        <v>402</v>
+      </c>
+      <c r="E50" t="s">
+        <v>513</v>
+      </c>
+      <c r="F50" t="s">
+        <v>514</v>
+      </c>
+      <c r="G50" t="s">
+        <v>515</v>
+      </c>
+      <c r="H50" t="s">
+        <v>406</v>
+      </c>
+      <c r="K50" t="s">
+        <v>515</v>
+      </c>
+      <c r="L50" t="s">
+        <v>585</v>
+      </c>
+      <c r="O50" t="s">
+        <v>510</v>
+      </c>
+      <c r="P50" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q50">
+        <v>17.119120438571215</v>
+      </c>
+      <c r="R50">
+        <v>51.213751122843391</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
+        <v>402</v>
+      </c>
+      <c r="E51" t="s">
+        <v>516</v>
+      </c>
+      <c r="F51" t="s">
+        <v>460</v>
+      </c>
+      <c r="G51" t="s">
+        <v>517</v>
+      </c>
+      <c r="H51" t="s">
+        <v>406</v>
+      </c>
+      <c r="K51" t="s">
+        <v>517</v>
+      </c>
+      <c r="L51" t="s">
+        <v>586</v>
+      </c>
+      <c r="O51" t="s">
+        <v>452</v>
+      </c>
+      <c r="P51" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q51">
+        <v>23.292570654205857</v>
+      </c>
+      <c r="R51">
+        <v>50.716735959213132</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>402</v>
+      </c>
+      <c r="E52" t="s">
+        <v>518</v>
+      </c>
+      <c r="F52" t="s">
+        <v>442</v>
+      </c>
+      <c r="G52" t="s">
+        <v>519</v>
+      </c>
+      <c r="H52" t="s">
+        <v>406</v>
+      </c>
+      <c r="K52" t="s">
+        <v>519</v>
+      </c>
+      <c r="L52" t="s">
+        <v>587</v>
+      </c>
+      <c r="O52" t="s">
+        <v>436</v>
+      </c>
+      <c r="P52" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52">
+        <v>15.292621647189277</v>
+      </c>
+      <c r="R52">
+        <v>51.988382273984612</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>402</v>
+      </c>
+      <c r="E53" t="s">
+        <v>507</v>
+      </c>
+      <c r="F53" t="s">
+        <v>520</v>
+      </c>
+      <c r="G53" t="s">
+        <v>521</v>
+      </c>
+      <c r="H53" t="s">
+        <v>406</v>
+      </c>
+      <c r="K53" t="s">
+        <v>521</v>
+      </c>
+      <c r="L53" t="s">
+        <v>588</v>
+      </c>
+      <c r="O53" t="s">
+        <v>460</v>
+      </c>
+      <c r="P53" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q53">
+        <v>18.254164899999999</v>
+      </c>
+      <c r="R53">
+        <v>50.376828600000003</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" t="s">
+        <v>402</v>
+      </c>
+      <c r="E54" t="s">
+        <v>507</v>
+      </c>
+      <c r="F54" t="s">
+        <v>522</v>
+      </c>
+      <c r="G54" t="s">
+        <v>523</v>
+      </c>
+      <c r="H54" t="s">
+        <v>406</v>
+      </c>
+      <c r="K54" t="s">
+        <v>523</v>
+      </c>
+      <c r="L54" t="s">
+        <v>589</v>
+      </c>
+      <c r="O54" t="s">
+        <v>511</v>
+      </c>
+      <c r="P54" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54">
+        <v>17.155532099999999</v>
+      </c>
+      <c r="R54">
+        <v>51.230800000000002</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>402</v>
+      </c>
+      <c r="E55" t="s">
+        <v>507</v>
+      </c>
+      <c r="F55" t="s">
+        <v>524</v>
+      </c>
+      <c r="G55" t="s">
+        <v>525</v>
+      </c>
+      <c r="H55" t="s">
+        <v>406</v>
+      </c>
+      <c r="K55" t="s">
+        <v>525</v>
+      </c>
+      <c r="L55" t="s">
+        <v>590</v>
+      </c>
+      <c r="O55" t="s">
+        <v>417</v>
+      </c>
+      <c r="P55" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q55">
+        <v>17.518080900000001</v>
+      </c>
+      <c r="R55">
+        <v>51.051585899999999</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" t="s">
+        <v>402</v>
+      </c>
+      <c r="E56" t="s">
+        <v>476</v>
+      </c>
+      <c r="F56" t="s">
+        <v>526</v>
+      </c>
+      <c r="G56" t="s">
+        <v>527</v>
+      </c>
+      <c r="H56" t="s">
+        <v>406</v>
+      </c>
+      <c r="K56" t="s">
+        <v>527</v>
+      </c>
+      <c r="L56" t="s">
+        <v>591</v>
+      </c>
+      <c r="O56" t="s">
+        <v>414</v>
+      </c>
+      <c r="P56" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q56">
+        <v>16.606215599999999</v>
+      </c>
+      <c r="R56">
+        <v>51.416170999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" t="s">
+        <v>402</v>
+      </c>
+      <c r="E57" t="s">
+        <v>483</v>
+      </c>
+      <c r="F57" t="s">
+        <v>528</v>
+      </c>
+      <c r="G57" t="s">
+        <v>529</v>
+      </c>
+      <c r="H57" t="s">
+        <v>406</v>
+      </c>
+      <c r="K57" t="s">
+        <v>529</v>
+      </c>
+      <c r="L57" t="s">
+        <v>592</v>
+      </c>
+      <c r="O57" t="s">
+        <v>420</v>
+      </c>
+      <c r="P57" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57">
+        <v>16.979750800000001</v>
+      </c>
+      <c r="R57">
+        <v>51.010129999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>402</v>
+      </c>
+      <c r="E58" t="s">
+        <v>438</v>
+      </c>
+      <c r="F58" t="s">
+        <v>530</v>
+      </c>
+      <c r="G58" t="s">
+        <v>531</v>
+      </c>
+      <c r="H58" t="s">
+        <v>406</v>
+      </c>
+      <c r="K58" t="s">
+        <v>531</v>
+      </c>
+      <c r="L58" t="s">
+        <v>593</v>
+      </c>
+      <c r="O58" t="s">
+        <v>408</v>
+      </c>
+      <c r="P58" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58">
+        <v>21.8027488</v>
+      </c>
+      <c r="R58">
+        <v>52.546132800000002</v>
+      </c>
+    </row>
+    <row r="59" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>402</v>
+      </c>
+      <c r="E59" t="s">
+        <v>438</v>
+      </c>
+      <c r="F59" t="s">
+        <v>532</v>
+      </c>
+      <c r="G59" t="s">
+        <v>533</v>
+      </c>
+      <c r="H59" t="s">
+        <v>406</v>
+      </c>
+      <c r="K59" t="s">
+        <v>533</v>
+      </c>
+      <c r="L59" t="s">
+        <v>594</v>
+      </c>
+      <c r="O59" t="s">
+        <v>538</v>
+      </c>
+      <c r="P59" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59">
+        <v>20.792006700000002</v>
+      </c>
+      <c r="R59">
+        <v>52.552813299999997</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>402</v>
+      </c>
+      <c r="E60" t="s">
+        <v>446</v>
+      </c>
+      <c r="F60" t="s">
+        <v>534</v>
+      </c>
+      <c r="G60" t="s">
+        <v>535</v>
+      </c>
+      <c r="H60" t="s">
+        <v>406</v>
+      </c>
+      <c r="K60" t="s">
+        <v>535</v>
+      </c>
+      <c r="L60" t="s">
+        <v>595</v>
+      </c>
+      <c r="O60" t="s">
+        <v>428</v>
+      </c>
+      <c r="P60" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60">
+        <v>20.550307400000001</v>
+      </c>
+      <c r="R60">
+        <v>53.504224899999997</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" t="s">
+        <v>402</v>
+      </c>
+      <c r="E61" t="s">
+        <v>438</v>
+      </c>
+      <c r="F61" t="s">
+        <v>536</v>
+      </c>
+      <c r="G61" t="s">
+        <v>537</v>
+      </c>
+      <c r="H61" t="s">
+        <v>406</v>
+      </c>
+      <c r="K61" t="s">
+        <v>537</v>
+      </c>
+      <c r="L61" t="s">
+        <v>596</v>
+      </c>
+      <c r="O61" t="s">
+        <v>520</v>
+      </c>
+      <c r="P61" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q61">
+        <v>20.022500000000001</v>
+      </c>
+      <c r="R61">
+        <v>52.509444440000003</v>
+      </c>
+    </row>
+    <row r="62" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
+        <v>402</v>
+      </c>
+      <c r="E62" t="s">
+        <v>488</v>
+      </c>
+      <c r="F62" t="s">
+        <v>538</v>
+      </c>
+      <c r="G62" t="s">
+        <v>539</v>
+      </c>
+      <c r="H62" t="s">
+        <v>406</v>
+      </c>
+      <c r="K62" t="s">
+        <v>539</v>
+      </c>
+      <c r="L62" t="s">
+        <v>597</v>
+      </c>
+      <c r="O62" t="s">
+        <v>522</v>
+      </c>
+      <c r="P62" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62">
+        <v>20.321666669999999</v>
+      </c>
+      <c r="R62">
+        <v>52.449166669999997</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O63" t="s">
+        <v>508</v>
+      </c>
+      <c r="P63" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q63">
+        <v>19.910833329999999</v>
+      </c>
+      <c r="R63">
+        <v>52.737777780000002</v>
+      </c>
+    </row>
+    <row r="64" spans="2:18" x14ac:dyDescent="0.45">
+      <c r="O64" t="s">
+        <v>524</v>
+      </c>
+      <c r="P64" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q64">
+        <v>19.910555559999999</v>
+      </c>
+      <c r="R64">
+        <v>52.738055559999999</v>
+      </c>
+    </row>
+    <row r="65" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O65" t="s">
+        <v>455</v>
+      </c>
+      <c r="P65" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q65">
+        <v>16.010833330000001</v>
+      </c>
+      <c r="R65">
+        <v>53.40138889</v>
+      </c>
+    </row>
+    <row r="66" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O66" t="s">
+        <v>477</v>
+      </c>
+      <c r="P66" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66">
+        <v>18.736666670000002</v>
+      </c>
+      <c r="R66">
+        <v>52.720833329999998</v>
+      </c>
+    </row>
+    <row r="67" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O67" t="s">
+        <v>526</v>
+      </c>
+      <c r="P67" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q67">
+        <v>18.420833330000001</v>
+      </c>
+      <c r="R67">
+        <v>52.663611109999998</v>
+      </c>
+    </row>
+    <row r="68" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O68" t="s">
+        <v>484</v>
+      </c>
+      <c r="P68" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q68">
+        <v>18.563333329999999</v>
+      </c>
+      <c r="R68">
+        <v>52.314166669999999</v>
+      </c>
+    </row>
+    <row r="69" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O69" t="s">
+        <v>528</v>
+      </c>
+      <c r="P69" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q69">
+        <v>18.581666670000001</v>
+      </c>
+      <c r="R69">
+        <v>52.072777780000003</v>
+      </c>
+    </row>
+    <row r="70" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O70" t="s">
+        <v>447</v>
+      </c>
+      <c r="P70" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q70">
+        <v>19.47555556</v>
+      </c>
+      <c r="R70">
+        <v>51.600555559999997</v>
+      </c>
+    </row>
+    <row r="71" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O71" t="s">
+        <v>442</v>
+      </c>
+      <c r="P71" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q71">
+        <v>20.966388890000001</v>
+      </c>
+      <c r="R71">
+        <v>51.883333329999999</v>
+      </c>
+    </row>
+    <row r="72" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O72" t="s">
+        <v>530</v>
+      </c>
+      <c r="P72" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72">
+        <v>15.046388889999999</v>
+      </c>
+      <c r="R72">
+        <v>53.63027778</v>
+      </c>
+    </row>
+    <row r="73" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O73" t="s">
+        <v>532</v>
+      </c>
+      <c r="P73" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q73">
+        <v>15.04666667</v>
+      </c>
+      <c r="R73">
+        <v>53.63</v>
+      </c>
+    </row>
+    <row r="74" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O74" t="s">
         <v>411</v>
       </c>
-      <c r="G6" t="s">
-        <v>412</v>
-      </c>
-      <c r="H6" t="s">
-        <v>409</v>
-      </c>
-      <c r="K6" t="s">
-        <v>412</v>
-      </c>
-      <c r="L6" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" t="s">
-        <v>413</v>
-      </c>
-      <c r="F7" t="s">
-        <v>414</v>
-      </c>
-      <c r="G7" t="s">
-        <v>415</v>
-      </c>
-      <c r="H7" t="s">
-        <v>409</v>
-      </c>
-      <c r="K7" t="s">
-        <v>415</v>
-      </c>
-      <c r="L7" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>405</v>
-      </c>
-      <c r="E8" t="s">
-        <v>416</v>
-      </c>
-      <c r="F8" t="s">
-        <v>417</v>
-      </c>
-      <c r="G8" t="s">
-        <v>418</v>
-      </c>
-      <c r="H8" t="s">
-        <v>409</v>
-      </c>
-      <c r="K8" t="s">
-        <v>418</v>
-      </c>
-      <c r="L8" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>405</v>
-      </c>
-      <c r="E9" t="s">
-        <v>419</v>
-      </c>
-      <c r="F9" t="s">
-        <v>420</v>
-      </c>
-      <c r="G9" t="s">
-        <v>421</v>
-      </c>
-      <c r="H9" t="s">
-        <v>409</v>
-      </c>
-      <c r="K9" t="s">
-        <v>421</v>
-      </c>
-      <c r="L9" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>405</v>
-      </c>
-      <c r="E10" t="s">
-        <v>422</v>
-      </c>
-      <c r="F10" t="s">
-        <v>423</v>
-      </c>
-      <c r="G10" t="s">
-        <v>424</v>
-      </c>
-      <c r="H10" t="s">
-        <v>409</v>
-      </c>
-      <c r="K10" t="s">
-        <v>424</v>
-      </c>
-      <c r="L10" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>405</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="P74" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q74">
+        <v>15.641666669999999</v>
+      </c>
+      <c r="R74">
+        <v>53.453888890000002</v>
+      </c>
+    </row>
+    <row r="75" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O75" t="s">
+        <v>534</v>
+      </c>
+      <c r="P75" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q75">
+        <v>19.30083333</v>
+      </c>
+      <c r="R75">
+        <v>51.814444440000003</v>
+      </c>
+    </row>
+    <row r="76" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O76" t="s">
         <v>425</v>
       </c>
-      <c r="F11" t="s">
-        <v>407</v>
-      </c>
-      <c r="G11" t="s">
-        <v>426</v>
-      </c>
-      <c r="H11" t="s">
-        <v>409</v>
-      </c>
-      <c r="K11" t="s">
-        <v>426</v>
-      </c>
-      <c r="L11" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>405</v>
-      </c>
-      <c r="E12" t="s">
-        <v>427</v>
-      </c>
-      <c r="F12" t="s">
-        <v>428</v>
-      </c>
-      <c r="G12" t="s">
-        <v>429</v>
-      </c>
-      <c r="H12" t="s">
-        <v>409</v>
-      </c>
-      <c r="K12" t="s">
-        <v>429</v>
-      </c>
-      <c r="L12" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>405</v>
-      </c>
-      <c r="E13" t="s">
-        <v>430</v>
-      </c>
-      <c r="F13" t="s">
-        <v>431</v>
-      </c>
-      <c r="G13" t="s">
-        <v>432</v>
-      </c>
-      <c r="H13" t="s">
-        <v>409</v>
-      </c>
-      <c r="K13" t="s">
-        <v>432</v>
-      </c>
-      <c r="L13" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" t="s">
-        <v>405</v>
-      </c>
-      <c r="E14" t="s">
-        <v>433</v>
-      </c>
-      <c r="F14" t="s">
-        <v>417</v>
-      </c>
-      <c r="G14" t="s">
-        <v>434</v>
-      </c>
-      <c r="H14" t="s">
-        <v>409</v>
-      </c>
-      <c r="K14" t="s">
-        <v>434</v>
-      </c>
-      <c r="L14" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" t="s">
-        <v>405</v>
-      </c>
-      <c r="E15" t="s">
-        <v>435</v>
-      </c>
-      <c r="F15" t="s">
-        <v>431</v>
-      </c>
-      <c r="G15" t="s">
-        <v>436</v>
-      </c>
-      <c r="H15" t="s">
-        <v>409</v>
-      </c>
-      <c r="K15" t="s">
-        <v>436</v>
-      </c>
-      <c r="L15" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" t="s">
-        <v>405</v>
-      </c>
-      <c r="E16" t="s">
-        <v>437</v>
-      </c>
-      <c r="F16" t="s">
-        <v>411</v>
-      </c>
-      <c r="G16" t="s">
-        <v>438</v>
-      </c>
-      <c r="H16" t="s">
-        <v>409</v>
-      </c>
-      <c r="K16" t="s">
-        <v>438</v>
-      </c>
-      <c r="L16" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" t="s">
-        <v>405</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="P76" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q76">
+        <v>15.578055559999999</v>
+      </c>
+      <c r="R76">
+        <v>53.685555559999997</v>
+      </c>
+    </row>
+    <row r="77" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O77" t="s">
+        <v>536</v>
+      </c>
+      <c r="P77" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q77">
+        <v>15.578055559999999</v>
+      </c>
+      <c r="R77">
+        <v>53.685555559999997</v>
+      </c>
+    </row>
+    <row r="78" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O78" t="s">
+        <v>404</v>
+      </c>
+      <c r="P78" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q78">
+        <v>18.143055560000001</v>
+      </c>
+      <c r="R78">
+        <v>52.946944440000003</v>
+      </c>
+    </row>
+    <row r="79" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O79" t="s">
         <v>439</v>
       </c>
-      <c r="F17" t="s">
-        <v>417</v>
-      </c>
-      <c r="G17" t="s">
-        <v>440</v>
-      </c>
-      <c r="H17" t="s">
-        <v>409</v>
-      </c>
-      <c r="K17" t="s">
-        <v>440</v>
-      </c>
-      <c r="L17" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" t="s">
-        <v>405</v>
-      </c>
-      <c r="E18" t="s">
-        <v>441</v>
-      </c>
-      <c r="F18" t="s">
-        <v>442</v>
-      </c>
-      <c r="G18" t="s">
-        <v>443</v>
-      </c>
-      <c r="H18" t="s">
-        <v>409</v>
-      </c>
-      <c r="K18" t="s">
-        <v>443</v>
-      </c>
-      <c r="L18" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" t="s">
-        <v>405</v>
-      </c>
-      <c r="E19" t="s">
-        <v>444</v>
-      </c>
-      <c r="F19" t="s">
-        <v>445</v>
-      </c>
-      <c r="G19" t="s">
-        <v>446</v>
-      </c>
-      <c r="H19" t="s">
-        <v>409</v>
-      </c>
-      <c r="K19" t="s">
-        <v>446</v>
-      </c>
-      <c r="L19" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" t="s">
-        <v>405</v>
-      </c>
-      <c r="E20" t="s">
-        <v>447</v>
-      </c>
-      <c r="F20" t="s">
-        <v>431</v>
-      </c>
-      <c r="G20" t="s">
-        <v>448</v>
-      </c>
-      <c r="H20" t="s">
-        <v>409</v>
-      </c>
-      <c r="K20" t="s">
-        <v>448</v>
-      </c>
-      <c r="L20" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>405</v>
-      </c>
-      <c r="E21" t="s">
-        <v>449</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="P79" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q79">
+        <v>14.509444439999999</v>
+      </c>
+      <c r="R79">
+        <v>53.654444439999999</v>
+      </c>
+    </row>
+    <row r="80" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O80" t="s">
+        <v>514</v>
+      </c>
+      <c r="P80" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q80">
+        <v>17.722777780000001</v>
+      </c>
+      <c r="R80">
+        <v>53.010833329999997</v>
+      </c>
+    </row>
+    <row r="81" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O81" t="s">
         <v>450</v>
       </c>
-      <c r="G21" t="s">
-        <v>451</v>
-      </c>
-      <c r="H21" t="s">
-        <v>409</v>
-      </c>
-      <c r="K21" t="s">
-        <v>451</v>
-      </c>
-      <c r="L21" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" t="s">
-        <v>405</v>
-      </c>
-      <c r="E22" t="s">
-        <v>452</v>
-      </c>
-      <c r="F22" t="s">
-        <v>453</v>
-      </c>
-      <c r="G22" t="s">
-        <v>454</v>
-      </c>
-      <c r="H22" t="s">
-        <v>409</v>
-      </c>
-      <c r="K22" t="s">
-        <v>454</v>
-      </c>
-      <c r="L22" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" t="s">
-        <v>405</v>
-      </c>
-      <c r="E23" t="s">
-        <v>455</v>
-      </c>
-      <c r="F23" t="s">
-        <v>445</v>
-      </c>
-      <c r="G23" t="s">
-        <v>456</v>
-      </c>
-      <c r="H23" t="s">
-        <v>409</v>
-      </c>
-      <c r="K23" t="s">
-        <v>456</v>
-      </c>
-      <c r="L23" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
-        <v>405</v>
-      </c>
-      <c r="E24" t="s">
-        <v>457</v>
-      </c>
-      <c r="F24" t="s">
-        <v>458</v>
-      </c>
-      <c r="G24" t="s">
-        <v>459</v>
-      </c>
-      <c r="H24" t="s">
-        <v>409</v>
-      </c>
-      <c r="K24" t="s">
-        <v>459</v>
-      </c>
-      <c r="L24" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>405</v>
-      </c>
-      <c r="E25" t="s">
-        <v>460</v>
-      </c>
-      <c r="F25" t="s">
-        <v>417</v>
-      </c>
-      <c r="G25" t="s">
-        <v>461</v>
-      </c>
-      <c r="H25" t="s">
-        <v>409</v>
-      </c>
-      <c r="K25" t="s">
-        <v>461</v>
-      </c>
-      <c r="L25" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" t="s">
-        <v>405</v>
-      </c>
-      <c r="E26" t="s">
-        <v>462</v>
-      </c>
-      <c r="F26" t="s">
-        <v>463</v>
-      </c>
-      <c r="G26" t="s">
-        <v>464</v>
-      </c>
-      <c r="H26" t="s">
-        <v>409</v>
-      </c>
-      <c r="K26" t="s">
-        <v>464</v>
-      </c>
-      <c r="L26" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" t="s">
-        <v>405</v>
-      </c>
-      <c r="E27" t="s">
-        <v>465</v>
-      </c>
-      <c r="F27" t="s">
-        <v>463</v>
-      </c>
-      <c r="G27" t="s">
-        <v>466</v>
-      </c>
-      <c r="H27" t="s">
-        <v>409</v>
-      </c>
-      <c r="K27" t="s">
-        <v>466</v>
-      </c>
-      <c r="L27" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" t="s">
-        <v>405</v>
-      </c>
-      <c r="E28" t="s">
-        <v>467</v>
-      </c>
-      <c r="F28" t="s">
-        <v>445</v>
-      </c>
-      <c r="G28" t="s">
-        <v>468</v>
-      </c>
-      <c r="H28" t="s">
-        <v>409</v>
-      </c>
-      <c r="K28" t="s">
-        <v>468</v>
-      </c>
-      <c r="L28" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" t="s">
-        <v>405</v>
-      </c>
-      <c r="E29" t="s">
-        <v>469</v>
-      </c>
-      <c r="F29" t="s">
-        <v>445</v>
-      </c>
-      <c r="G29" t="s">
-        <v>470</v>
-      </c>
-      <c r="H29" t="s">
-        <v>409</v>
-      </c>
-      <c r="K29" t="s">
-        <v>470</v>
-      </c>
-      <c r="L29" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" t="s">
-        <v>405</v>
-      </c>
-      <c r="E30" t="s">
-        <v>471</v>
-      </c>
-      <c r="F30" t="s">
-        <v>450</v>
-      </c>
-      <c r="G30" t="s">
-        <v>472</v>
-      </c>
-      <c r="H30" t="s">
-        <v>409</v>
-      </c>
-      <c r="K30" t="s">
-        <v>472</v>
-      </c>
-      <c r="L30" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" t="s">
-        <v>405</v>
-      </c>
-      <c r="E31" t="s">
-        <v>473</v>
-      </c>
-      <c r="F31" t="s">
-        <v>445</v>
-      </c>
-      <c r="G31" t="s">
-        <v>474</v>
-      </c>
-      <c r="H31" t="s">
-        <v>409</v>
-      </c>
-      <c r="K31" t="s">
-        <v>474</v>
-      </c>
-      <c r="L31" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" t="s">
-        <v>405</v>
-      </c>
-      <c r="E32" t="s">
-        <v>475</v>
-      </c>
-      <c r="F32" t="s">
-        <v>445</v>
-      </c>
-      <c r="G32" t="s">
-        <v>476</v>
-      </c>
-      <c r="H32" t="s">
-        <v>409</v>
-      </c>
-      <c r="K32" t="s">
-        <v>476</v>
-      </c>
-      <c r="L32" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" t="s">
-        <v>405</v>
-      </c>
-      <c r="E33" t="s">
-        <v>477</v>
-      </c>
-      <c r="F33" t="s">
-        <v>453</v>
-      </c>
-      <c r="G33" t="s">
-        <v>478</v>
-      </c>
-      <c r="H33" t="s">
-        <v>409</v>
-      </c>
-      <c r="K33" t="s">
-        <v>478</v>
-      </c>
-      <c r="L33" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" t="s">
-        <v>405</v>
-      </c>
-      <c r="E34" t="s">
-        <v>479</v>
-      </c>
-      <c r="F34" t="s">
-        <v>480</v>
-      </c>
-      <c r="G34" t="s">
-        <v>481</v>
-      </c>
-      <c r="H34" t="s">
-        <v>409</v>
-      </c>
-      <c r="K34" t="s">
-        <v>481</v>
-      </c>
-      <c r="L34" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" t="s">
-        <v>405</v>
-      </c>
-      <c r="E35" t="s">
-        <v>482</v>
-      </c>
-      <c r="F35" t="s">
-        <v>445</v>
-      </c>
-      <c r="G35" t="s">
-        <v>483</v>
-      </c>
-      <c r="H35" t="s">
-        <v>409</v>
-      </c>
-      <c r="K35" t="s">
-        <v>483</v>
-      </c>
-      <c r="L35" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" t="s">
-        <v>405</v>
-      </c>
-      <c r="E36" t="s">
-        <v>484</v>
-      </c>
-      <c r="F36" t="s">
-        <v>420</v>
-      </c>
-      <c r="G36" t="s">
-        <v>485</v>
-      </c>
-      <c r="H36" t="s">
-        <v>409</v>
-      </c>
-      <c r="K36" t="s">
-        <v>485</v>
-      </c>
-      <c r="L36" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" t="s">
-        <v>405</v>
-      </c>
-      <c r="E37" t="s">
-        <v>486</v>
-      </c>
-      <c r="F37" t="s">
-        <v>487</v>
-      </c>
-      <c r="G37" t="s">
-        <v>488</v>
-      </c>
-      <c r="H37" t="s">
-        <v>409</v>
-      </c>
-      <c r="K37" t="s">
-        <v>488</v>
-      </c>
-      <c r="L37" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" t="s">
-        <v>405</v>
-      </c>
-      <c r="E38" t="s">
-        <v>489</v>
-      </c>
-      <c r="F38" t="s">
-        <v>428</v>
-      </c>
-      <c r="G38" t="s">
-        <v>490</v>
-      </c>
-      <c r="H38" t="s">
-        <v>409</v>
-      </c>
-      <c r="K38" t="s">
-        <v>490</v>
-      </c>
-      <c r="L38" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" t="s">
-        <v>405</v>
-      </c>
-      <c r="E39" t="s">
-        <v>491</v>
-      </c>
-      <c r="F39" t="s">
-        <v>445</v>
-      </c>
-      <c r="G39" t="s">
-        <v>492</v>
-      </c>
-      <c r="H39" t="s">
-        <v>409</v>
-      </c>
-      <c r="K39" t="s">
-        <v>492</v>
-      </c>
-      <c r="L39" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B40" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" t="s">
-        <v>405</v>
-      </c>
-      <c r="E40" t="s">
-        <v>493</v>
-      </c>
-      <c r="F40" t="s">
-        <v>463</v>
-      </c>
-      <c r="G40" t="s">
-        <v>494</v>
-      </c>
-      <c r="H40" t="s">
-        <v>409</v>
-      </c>
-      <c r="K40" t="s">
-        <v>494</v>
-      </c>
-      <c r="L40" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B41" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" t="s">
-        <v>405</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="P81" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81">
+        <v>18.771666669999998</v>
+      </c>
+      <c r="R81">
+        <v>51.447777780000003</v>
+      </c>
+    </row>
+    <row r="82" spans="15:18" x14ac:dyDescent="0.45">
+      <c r="O82" t="s">
         <v>495</v>
       </c>
-      <c r="F41" t="s">
-        <v>431</v>
-      </c>
-      <c r="G41" t="s">
-        <v>496</v>
-      </c>
-      <c r="H41" t="s">
-        <v>409</v>
-      </c>
-      <c r="K41" t="s">
-        <v>496</v>
-      </c>
-      <c r="L41" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" t="s">
-        <v>405</v>
-      </c>
-      <c r="E42" t="s">
-        <v>497</v>
-      </c>
-      <c r="F42" t="s">
-        <v>498</v>
-      </c>
-      <c r="G42" t="s">
-        <v>499</v>
-      </c>
-      <c r="H42" t="s">
-        <v>409</v>
-      </c>
-      <c r="K42" t="s">
-        <v>499</v>
-      </c>
-      <c r="L42" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B43" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" t="s">
-        <v>405</v>
-      </c>
-      <c r="E43" t="s">
-        <v>500</v>
-      </c>
-      <c r="F43" t="s">
-        <v>463</v>
-      </c>
-      <c r="G43" t="s">
-        <v>501</v>
-      </c>
-      <c r="H43" t="s">
-        <v>409</v>
-      </c>
-      <c r="K43" t="s">
-        <v>501</v>
-      </c>
-      <c r="L43" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" t="s">
-        <v>405</v>
-      </c>
-      <c r="E44" t="s">
-        <v>502</v>
-      </c>
-      <c r="F44" t="s">
-        <v>442</v>
-      </c>
-      <c r="G44" t="s">
-        <v>503</v>
-      </c>
-      <c r="H44" t="s">
-        <v>409</v>
-      </c>
-      <c r="K44" t="s">
-        <v>503</v>
-      </c>
-      <c r="L44" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" t="s">
-        <v>405</v>
-      </c>
-      <c r="E45" t="s">
-        <v>504</v>
-      </c>
-      <c r="F45" t="s">
-        <v>463</v>
-      </c>
-      <c r="G45" t="s">
-        <v>505</v>
-      </c>
-      <c r="H45" t="s">
-        <v>409</v>
-      </c>
-      <c r="K45" t="s">
-        <v>505</v>
-      </c>
-      <c r="L45" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" t="s">
-        <v>405</v>
-      </c>
-      <c r="E46" t="s">
-        <v>506</v>
-      </c>
-      <c r="F46" t="s">
-        <v>463</v>
-      </c>
-      <c r="G46" t="s">
-        <v>507</v>
-      </c>
-      <c r="H46" t="s">
-        <v>409</v>
-      </c>
-      <c r="K46" t="s">
-        <v>507</v>
-      </c>
-      <c r="L46" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" t="s">
-        <v>405</v>
-      </c>
-      <c r="E47" t="s">
-        <v>508</v>
-      </c>
-      <c r="F47" t="s">
-        <v>407</v>
-      </c>
-      <c r="G47" t="s">
-        <v>509</v>
-      </c>
-      <c r="H47" t="s">
-        <v>409</v>
-      </c>
-      <c r="K47" t="s">
-        <v>509</v>
-      </c>
-      <c r="L47" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" t="s">
-        <v>405</v>
-      </c>
-      <c r="E48" t="s">
-        <v>510</v>
-      </c>
-      <c r="F48" t="s">
-        <v>511</v>
-      </c>
-      <c r="G48" t="s">
-        <v>512</v>
-      </c>
-      <c r="H48" t="s">
-        <v>409</v>
-      </c>
-      <c r="K48" t="s">
-        <v>512</v>
-      </c>
-      <c r="L48" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B49" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" t="s">
-        <v>405</v>
-      </c>
-      <c r="E49" t="s">
-        <v>513</v>
-      </c>
-      <c r="F49" t="s">
-        <v>514</v>
-      </c>
-      <c r="G49" t="s">
-        <v>515</v>
-      </c>
-      <c r="H49" t="s">
-        <v>409</v>
-      </c>
-      <c r="K49" t="s">
-        <v>515</v>
-      </c>
-      <c r="L49" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" t="s">
-        <v>405</v>
-      </c>
-      <c r="E50" t="s">
-        <v>516</v>
-      </c>
-      <c r="F50" t="s">
-        <v>517</v>
-      </c>
-      <c r="G50" t="s">
-        <v>518</v>
-      </c>
-      <c r="H50" t="s">
-        <v>409</v>
-      </c>
-      <c r="K50" t="s">
-        <v>518</v>
-      </c>
-      <c r="L50" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" t="s">
-        <v>405</v>
-      </c>
-      <c r="E51" t="s">
-        <v>519</v>
-      </c>
-      <c r="F51" t="s">
-        <v>463</v>
-      </c>
-      <c r="G51" t="s">
-        <v>520</v>
-      </c>
-      <c r="H51" t="s">
-        <v>409</v>
-      </c>
-      <c r="K51" t="s">
-        <v>520</v>
-      </c>
-      <c r="L51" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" t="s">
-        <v>405</v>
-      </c>
-      <c r="E52" t="s">
-        <v>521</v>
-      </c>
-      <c r="F52" t="s">
-        <v>445</v>
-      </c>
-      <c r="G52" t="s">
-        <v>522</v>
-      </c>
-      <c r="H52" t="s">
-        <v>409</v>
-      </c>
-      <c r="K52" t="s">
-        <v>522</v>
-      </c>
-      <c r="L52" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" t="s">
-        <v>405</v>
-      </c>
-      <c r="E53" t="s">
-        <v>510</v>
-      </c>
-      <c r="F53" t="s">
-        <v>523</v>
-      </c>
-      <c r="G53" t="s">
-        <v>524</v>
-      </c>
-      <c r="H53" t="s">
-        <v>409</v>
-      </c>
-      <c r="K53" t="s">
-        <v>524</v>
-      </c>
-      <c r="L53" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" t="s">
-        <v>405</v>
-      </c>
-      <c r="E54" t="s">
-        <v>510</v>
-      </c>
-      <c r="F54" t="s">
-        <v>525</v>
-      </c>
-      <c r="G54" t="s">
-        <v>526</v>
-      </c>
-      <c r="H54" t="s">
-        <v>409</v>
-      </c>
-      <c r="K54" t="s">
-        <v>526</v>
-      </c>
-      <c r="L54" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" t="s">
-        <v>405</v>
-      </c>
-      <c r="E55" t="s">
-        <v>510</v>
-      </c>
-      <c r="F55" t="s">
-        <v>527</v>
-      </c>
-      <c r="G55" t="s">
-        <v>528</v>
-      </c>
-      <c r="H55" t="s">
-        <v>409</v>
-      </c>
-      <c r="K55" t="s">
-        <v>528</v>
-      </c>
-      <c r="L55" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B56" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" t="s">
-        <v>405</v>
-      </c>
-      <c r="E56" t="s">
-        <v>479</v>
-      </c>
-      <c r="F56" t="s">
-        <v>529</v>
-      </c>
-      <c r="G56" t="s">
-        <v>530</v>
-      </c>
-      <c r="H56" t="s">
-        <v>409</v>
-      </c>
-      <c r="K56" t="s">
-        <v>530</v>
-      </c>
-      <c r="L56" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" t="s">
-        <v>405</v>
-      </c>
-      <c r="E57" t="s">
-        <v>486</v>
-      </c>
-      <c r="F57" t="s">
-        <v>531</v>
-      </c>
-      <c r="G57" t="s">
-        <v>532</v>
-      </c>
-      <c r="H57" t="s">
-        <v>409</v>
-      </c>
-      <c r="K57" t="s">
-        <v>532</v>
-      </c>
-      <c r="L57" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" t="s">
-        <v>405</v>
-      </c>
-      <c r="E58" t="s">
-        <v>441</v>
-      </c>
-      <c r="F58" t="s">
-        <v>533</v>
-      </c>
-      <c r="G58" t="s">
-        <v>534</v>
-      </c>
-      <c r="H58" t="s">
-        <v>409</v>
-      </c>
-      <c r="K58" t="s">
-        <v>534</v>
-      </c>
-      <c r="L58" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" t="s">
-        <v>405</v>
-      </c>
-      <c r="E59" t="s">
-        <v>441</v>
-      </c>
-      <c r="F59" t="s">
-        <v>535</v>
-      </c>
-      <c r="G59" t="s">
-        <v>536</v>
-      </c>
-      <c r="H59" t="s">
-        <v>409</v>
-      </c>
-      <c r="K59" t="s">
-        <v>536</v>
-      </c>
-      <c r="L59" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B60" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" t="s">
-        <v>405</v>
-      </c>
-      <c r="E60" t="s">
-        <v>449</v>
-      </c>
-      <c r="F60" t="s">
-        <v>537</v>
-      </c>
-      <c r="G60" t="s">
-        <v>538</v>
-      </c>
-      <c r="H60" t="s">
-        <v>409</v>
-      </c>
-      <c r="K60" t="s">
-        <v>538</v>
-      </c>
-      <c r="L60" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B61" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" t="s">
-        <v>405</v>
-      </c>
-      <c r="E61" t="s">
-        <v>441</v>
-      </c>
-      <c r="F61" t="s">
-        <v>539</v>
-      </c>
-      <c r="G61" t="s">
-        <v>540</v>
-      </c>
-      <c r="H61" t="s">
-        <v>409</v>
-      </c>
-      <c r="K61" t="s">
-        <v>540</v>
-      </c>
-      <c r="L61" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B62" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" t="s">
-        <v>405</v>
-      </c>
-      <c r="E62" t="s">
-        <v>491</v>
-      </c>
-      <c r="F62" t="s">
-        <v>541</v>
-      </c>
-      <c r="G62" t="s">
-        <v>542</v>
-      </c>
-      <c r="H62" t="s">
-        <v>409</v>
-      </c>
-      <c r="K62" t="s">
-        <v>542</v>
-      </c>
-      <c r="L62" t="s">
-        <v>600</v>
+      <c r="P82" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q82">
+        <v>17.051111110000001</v>
+      </c>
+      <c r="R82">
+        <v>52.446111109999997</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66E674CA-9203-4537-9B76-17EFF7F696D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89C249BB-E01E-4326-B9E5-C4487345A364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{C95DAEBB-B4C5-4D8C-8F5E-6151049A2959}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{AEE4F3D3-F15F-44CC-9855-55ECE7C36879}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8EBDD39-F66C-4E10-97EE-F9F8139D955A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91E00B17-24E1-4C1E-A229-294E9840E479}">
   <dimension ref="B3:S166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7468,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3229CCB-B8B1-4D98-81D6-1198B9E7A869}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9FA86A-E525-41B2-9A89-D3CA860F1CB7}">
   <dimension ref="B3:S72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89C249BB-E01E-4326-B9E5-C4487345A364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65301F87-7079-4FF0-88BD-6DE54516D253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{AEE4F3D3-F15F-44CC-9855-55ECE7C36879}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{780CE602-017A-495B-B1D5-3434ABE1EA39}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91E00B17-24E1-4C1E-A229-294E9840E479}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D79D05A-0D0E-4F33-82BE-44D6894149EA}">
   <dimension ref="B3:S166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7468,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9FA86A-E525-41B2-9A89-D3CA860F1CB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F491C34-231F-4F7A-AAE3-6EBC3111E920}">
   <dimension ref="B3:S72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65301F87-7079-4FF0-88BD-6DE54516D253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84C7E960-6F46-4B7E-9902-E51482EBC36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{780CE602-017A-495B-B1D5-3434ABE1EA39}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{C6E52B7B-82ED-4117-A649-F517544DD6A3}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D79D05A-0D0E-4F33-82BE-44D6894149EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE084D9-EB4F-401C-B91E-0C5E67E439A6}">
   <dimension ref="B3:S166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7468,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F491C34-231F-4F7A-AAE3-6EBC3111E920}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5598701A-182C-4B69-BF48-1E6B510AC2D2}">
   <dimension ref="B3:S72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84C7E960-6F46-4B7E-9902-E51482EBC36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C157EAEA-B698-407B-BECF-8BEB05CC25C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{C6E52B7B-82ED-4117-A649-F517544DD6A3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{5059B29A-C127-44D2-A04D-21EED8AC43F9}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE084D9-EB4F-401C-B91E-0C5E67E439A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF542F00-2905-4A2B-AF08-92DF76E2EE2E}">
   <dimension ref="B3:S166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7468,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5598701A-182C-4B69-BF48-1E6B510AC2D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CF7C12-0DEC-4A15-BE69-05EF465DB542}">
   <dimension ref="B3:S72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C157EAEA-B698-407B-BECF-8BEB05CC25C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35B83FC0-1C1F-4A63-80C8-709CCF1D5E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{5059B29A-C127-44D2-A04D-21EED8AC43F9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{E5A79496-40D6-4293-92EF-E9512977A288}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF542F00-2905-4A2B-AF08-92DF76E2EE2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A84FF3-DA21-4F64-B27E-4EB08267E26C}">
   <dimension ref="B3:S166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7468,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17CF7C12-0DEC-4A15-BE69-05EF465DB542}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14CF6A4-2296-4B14-89F4-81DF42F4E67E}">
   <dimension ref="B3:S72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35B83FC0-1C1F-4A63-80C8-709CCF1D5E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD07CFC2-50ED-4F40-8364-CE15F8657464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{E5A79496-40D6-4293-92EF-E9512977A288}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{22604F60-86BD-4C2B-BB11-29345045EDDD}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A84FF3-DA21-4F64-B27E-4EB08267E26C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB43F01-27B8-409E-998B-6EC9299225B4}">
   <dimension ref="B3:S166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7468,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14CF6A4-2296-4B14-89F4-81DF42F4E67E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A75492-3B5D-4FAC-A28C-4771FC5C0DE9}">
   <dimension ref="B3:S72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD07CFC2-50ED-4F40-8364-CE15F8657464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{216C262F-F178-4C7E-AE32-583847102FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{22604F60-86BD-4C2B-BB11-29345045EDDD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{D0415AC1-5F64-4163-A3C5-C01DAC2D2E1C}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -2267,7 +2267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAB43F01-27B8-409E-998B-6EC9299225B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032E8560-05EC-4C9A-8632-9C7A15C7510E}">
   <dimension ref="B3:S166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7468,7 +7468,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36A75492-3B5D-4FAC-A28C-4771FC5C0DE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64809CCE-EDE6-48C1-BB47-B61B06F56DFF}">
   <dimension ref="B3:S72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
